--- a/AmbermoonAdvanced.xlsx
+++ b/AmbermoonAdvanced.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Robert\source\repos\Ambermoon-Advanced\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CECAA5ED-8AB8-483C-B045-1C54FC62CFAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B78E65F9-377B-4CA0-B59F-5A795E2AF2FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="6" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3150" uniqueCount="2269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3152" uniqueCount="2271">
   <si>
     <t>Map texts</t>
   </si>
@@ -7042,6 +7042,12 @@
   </si>
   <si>
     <t>Remake Branch aa4-fixes: CLI für Tests (--data, --skip-intro, --load 0, --cheat, --screenshot, --exit-after). Testdaten: tools/ambtools/make_testdata.py</t>
+  </si>
+  <si>
+    <t>Englisch: alle 244 neuen Ep4-Texte übersetzt (english/Amberfiles/AllTexts, Quelle tools/translations/ep4_english.py). Bitte gegenlesen. Neue deutsche Texte später ebenfalls nachziehen.</t>
+  </si>
+  <si>
+    <t>Wise man house Stühle: Screenshots aus dem Remake vorhanden, Vergleich mit Amiga steht noch aus.</t>
   </si>
 </sst>
 </file>
@@ -7696,17 +7702,17 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -16970,14 +16976,14 @@
       <c r="B32" s="54" t="s">
         <v>1831</v>
       </c>
-      <c r="C32" s="79" t="s">
+      <c r="C32" s="76" t="s">
         <v>1832</v>
       </c>
-      <c r="D32" s="79"/>
-      <c r="E32" s="79"/>
-      <c r="F32" s="79"/>
-      <c r="G32" s="79"/>
-      <c r="H32" s="79"/>
+      <c r="D32" s="76"/>
+      <c r="E32" s="76"/>
+      <c r="F32" s="76"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="76"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="36" t="s">
@@ -16986,14 +16992,14 @@
       <c r="B33" s="28" t="s">
         <v>1834</v>
       </c>
-      <c r="C33" s="78" t="s">
+      <c r="C33" s="77" t="s">
         <v>1835</v>
       </c>
-      <c r="D33" s="78"/>
-      <c r="E33" s="78"/>
-      <c r="F33" s="78"/>
-      <c r="G33" s="78"/>
-      <c r="H33" s="78"/>
+      <c r="D33" s="77"/>
+      <c r="E33" s="77"/>
+      <c r="F33" s="77"/>
+      <c r="G33" s="77"/>
+      <c r="H33" s="77"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="36" t="s">
@@ -17002,14 +17008,14 @@
       <c r="B34" s="28" t="s">
         <v>1834</v>
       </c>
-      <c r="C34" s="78" t="s">
+      <c r="C34" s="77" t="s">
         <v>1835</v>
       </c>
-      <c r="D34" s="78"/>
-      <c r="E34" s="78"/>
-      <c r="F34" s="78"/>
-      <c r="G34" s="78"/>
-      <c r="H34" s="78"/>
+      <c r="D34" s="77"/>
+      <c r="E34" s="77"/>
+      <c r="F34" s="77"/>
+      <c r="G34" s="77"/>
+      <c r="H34" s="77"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="36" t="s">
@@ -17018,14 +17024,14 @@
       <c r="B35" s="28" t="s">
         <v>1834</v>
       </c>
-      <c r="C35" s="78" t="s">
+      <c r="C35" s="77" t="s">
         <v>1835</v>
       </c>
-      <c r="D35" s="78"/>
-      <c r="E35" s="78"/>
-      <c r="F35" s="78"/>
-      <c r="G35" s="78"/>
-      <c r="H35" s="78"/>
+      <c r="D35" s="77"/>
+      <c r="E35" s="77"/>
+      <c r="F35" s="77"/>
+      <c r="G35" s="77"/>
+      <c r="H35" s="77"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="36" t="s">
@@ -17034,14 +17040,14 @@
       <c r="B36" s="28" t="s">
         <v>1820</v>
       </c>
-      <c r="C36" s="77" t="s">
+      <c r="C36" s="78" t="s">
         <v>1839</v>
       </c>
-      <c r="D36" s="77"/>
-      <c r="E36" s="77"/>
-      <c r="F36" s="77"/>
-      <c r="G36" s="77"/>
-      <c r="H36" s="77"/>
+      <c r="D36" s="78"/>
+      <c r="E36" s="78"/>
+      <c r="F36" s="78"/>
+      <c r="G36" s="78"/>
+      <c r="H36" s="78"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="36" t="s">
@@ -17050,14 +17056,14 @@
       <c r="B37" s="28" t="s">
         <v>1822</v>
       </c>
-      <c r="C37" s="78" t="s">
+      <c r="C37" s="77" t="s">
         <v>1841</v>
       </c>
-      <c r="D37" s="78"/>
-      <c r="E37" s="78"/>
-      <c r="F37" s="78"/>
-      <c r="G37" s="78"/>
-      <c r="H37" s="78"/>
+      <c r="D37" s="77"/>
+      <c r="E37" s="77"/>
+      <c r="F37" s="77"/>
+      <c r="G37" s="77"/>
+      <c r="H37" s="77"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="36" t="s">
@@ -17066,14 +17072,14 @@
       <c r="B38" s="28" t="s">
         <v>1820</v>
       </c>
-      <c r="C38" s="78" t="s">
+      <c r="C38" s="77" t="s">
         <v>1841</v>
       </c>
-      <c r="D38" s="78"/>
-      <c r="E38" s="78"/>
-      <c r="F38" s="78"/>
-      <c r="G38" s="78"/>
-      <c r="H38" s="78"/>
+      <c r="D38" s="77"/>
+      <c r="E38" s="77"/>
+      <c r="F38" s="77"/>
+      <c r="G38" s="77"/>
+      <c r="H38" s="77"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="36" t="s">
@@ -17082,14 +17088,14 @@
       <c r="B39" s="28" t="s">
         <v>1820</v>
       </c>
-      <c r="C39" s="77" t="s">
+      <c r="C39" s="78" t="s">
         <v>1839</v>
       </c>
-      <c r="D39" s="77"/>
-      <c r="E39" s="77"/>
-      <c r="F39" s="77"/>
-      <c r="G39" s="77"/>
-      <c r="H39" s="77"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="36" t="s">
@@ -17098,14 +17104,14 @@
       <c r="B40" s="28" t="s">
         <v>1820</v>
       </c>
-      <c r="C40" s="77" t="s">
+      <c r="C40" s="78" t="s">
         <v>1839</v>
       </c>
-      <c r="D40" s="77"/>
-      <c r="E40" s="77"/>
-      <c r="F40" s="77"/>
-      <c r="G40" s="77"/>
-      <c r="H40" s="77"/>
+      <c r="D40" s="78"/>
+      <c r="E40" s="78"/>
+      <c r="F40" s="78"/>
+      <c r="G40" s="78"/>
+      <c r="H40" s="78"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="36" t="s">
@@ -17114,14 +17120,14 @@
       <c r="B41" s="28" t="s">
         <v>1823</v>
       </c>
-      <c r="C41" s="77" t="s">
+      <c r="C41" s="78" t="s">
         <v>1845</v>
       </c>
-      <c r="D41" s="77"/>
-      <c r="E41" s="77"/>
-      <c r="F41" s="77"/>
-      <c r="G41" s="77"/>
-      <c r="H41" s="77"/>
+      <c r="D41" s="78"/>
+      <c r="E41" s="78"/>
+      <c r="F41" s="78"/>
+      <c r="G41" s="78"/>
+      <c r="H41" s="78"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="36" t="s">
@@ -17130,14 +17136,14 @@
       <c r="B42" s="28" t="s">
         <v>1824</v>
       </c>
-      <c r="C42" s="77" t="s">
+      <c r="C42" s="78" t="s">
         <v>1847</v>
       </c>
-      <c r="D42" s="77"/>
-      <c r="E42" s="77"/>
-      <c r="F42" s="77"/>
-      <c r="G42" s="77"/>
-      <c r="H42" s="77"/>
+      <c r="D42" s="78"/>
+      <c r="E42" s="78"/>
+      <c r="F42" s="78"/>
+      <c r="G42" s="78"/>
+      <c r="H42" s="78"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="36" t="s">
@@ -17146,14 +17152,14 @@
       <c r="B43" s="28" t="s">
         <v>1825</v>
       </c>
-      <c r="C43" s="77" t="s">
+      <c r="C43" s="78" t="s">
         <v>1849</v>
       </c>
-      <c r="D43" s="77"/>
-      <c r="E43" s="77"/>
-      <c r="F43" s="77"/>
-      <c r="G43" s="77"/>
-      <c r="H43" s="77"/>
+      <c r="D43" s="78"/>
+      <c r="E43" s="78"/>
+      <c r="F43" s="78"/>
+      <c r="G43" s="78"/>
+      <c r="H43" s="78"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="36" t="s">
@@ -17162,26 +17168,26 @@
       <c r="B44" s="28" t="s">
         <v>1826</v>
       </c>
-      <c r="C44" s="77" t="s">
+      <c r="C44" s="78" t="s">
         <v>1851</v>
       </c>
-      <c r="D44" s="77"/>
-      <c r="E44" s="77"/>
-      <c r="F44" s="77"/>
-      <c r="G44" s="77"/>
-      <c r="H44" s="77"/>
+      <c r="D44" s="78"/>
+      <c r="E44" s="78"/>
+      <c r="F44" s="78"/>
+      <c r="G44" s="78"/>
+      <c r="H44" s="78"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="76" t="s">
+      <c r="A48" s="79" t="s">
         <v>1840</v>
       </c>
-      <c r="B48" s="76"/>
-      <c r="C48" s="76"/>
-      <c r="D48" s="76"/>
-      <c r="E48" s="76"/>
-      <c r="F48" s="76"/>
-      <c r="G48" s="76"/>
-      <c r="H48" s="76"/>
+      <c r="B48" s="79"/>
+      <c r="C48" s="79"/>
+      <c r="D48" s="79"/>
+      <c r="E48" s="79"/>
+      <c r="F48" s="79"/>
+      <c r="G48" s="79"/>
+      <c r="H48" s="79"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
@@ -17194,16 +17200,16 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="76" t="s">
+      <c r="A52" s="79" t="s">
         <v>1842</v>
       </c>
-      <c r="B52" s="76"/>
-      <c r="C52" s="76"/>
-      <c r="D52" s="76"/>
-      <c r="E52" s="76"/>
-      <c r="F52" s="76"/>
-      <c r="G52" s="76"/>
-      <c r="H52" s="76"/>
+      <c r="B52" s="79"/>
+      <c r="C52" s="79"/>
+      <c r="D52" s="79"/>
+      <c r="E52" s="79"/>
+      <c r="F52" s="79"/>
+      <c r="G52" s="79"/>
+      <c r="H52" s="79"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -17211,16 +17217,16 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="76" t="s">
+      <c r="A57" s="79" t="s">
         <v>1855</v>
       </c>
-      <c r="B57" s="76"/>
-      <c r="C57" s="76"/>
-      <c r="D57" s="76"/>
-      <c r="E57" s="76"/>
-      <c r="F57" s="76"/>
-      <c r="G57" s="76"/>
-      <c r="H57" s="76"/>
+      <c r="B57" s="79"/>
+      <c r="C57" s="79"/>
+      <c r="D57" s="79"/>
+      <c r="E57" s="79"/>
+      <c r="F57" s="79"/>
+      <c r="G57" s="79"/>
+      <c r="H57" s="79"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
@@ -17288,12 +17294,12 @@
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H73" s="76" t="s">
+      <c r="H73" s="79" t="s">
         <v>1869</v>
       </c>
-      <c r="I73" s="76"/>
-      <c r="J73" s="76"/>
-      <c r="K73" s="76"/>
+      <c r="I73" s="79"/>
+      <c r="J73" s="79"/>
+      <c r="K73" s="79"/>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="55" t="s">
@@ -17860,16 +17866,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="C32:H32"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="C35:H35"/>
-    <mergeCell ref="C36:H36"/>
-    <mergeCell ref="C37:H37"/>
-    <mergeCell ref="C38:H38"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C40:H40"/>
-    <mergeCell ref="C41:H41"/>
     <mergeCell ref="A57:H57"/>
     <mergeCell ref="H73:K73"/>
     <mergeCell ref="C42:H42"/>
@@ -17877,6 +17873,16 @@
     <mergeCell ref="C44:H44"/>
     <mergeCell ref="A48:H48"/>
     <mergeCell ref="A52:H52"/>
+    <mergeCell ref="C37:H37"/>
+    <mergeCell ref="C38:H38"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
+    <mergeCell ref="C41:H41"/>
+    <mergeCell ref="C32:H32"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="C35:H35"/>
+    <mergeCell ref="C36:H36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -17939,13 +17945,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="79" t="s">
         <v>1991</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
@@ -20927,7 +20933,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B116"/>
+  <dimension ref="A1:B118"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -20995,411 +21001,421 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>2267</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>2268</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>2230</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>2231</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
+        <v>2231</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
         <v>2228</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="68" t="s">
-        <v>2227</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="68" t="s">
-        <v>2229</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="68" t="s">
+        <v>2227</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="68" t="s">
+        <v>2229</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="68" t="s">
         <v>2265</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="68" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="68" t="s">
         <v>2262</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>67</v>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="68" t="s">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="68" t="s">
         <v>2266</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="4" t="s">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="55" spans="1:1" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+    <row r="57" spans="1:1" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>91</v>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>94</v>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
         <v>98</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="4" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>102</v>
+      <c r="A84" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>104</v>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>111</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" s="4" t="s">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="s">
         <v>113</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" s="4" t="s">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="4" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
         <v>129</v>
       </c>
     </row>

--- a/AmbermoonAdvanced.xlsx
+++ b/AmbermoonAdvanced.xlsx
@@ -20937,495 +20937,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B119"/>
+  <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
-        <v>2267</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
-        <v>2268</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
-        <v>2265</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
-        <v>2266</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
-        <v>2228</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
-        <v>2229</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
-        <v>2226</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="68" t="s">
-        <v>2225</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="68" t="s">
-        <v>2227</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="68" t="s">
-        <v>2263</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="68" t="s">
-        <v>2260</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="68" t="s">
-        <v>2269</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="68" t="s">
-        <v>2264</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" s="68" t="s">
-        <v>2270</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" s="82" t="s">
-        <v>2271</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>127</v>
+    <row r="1" spans="1:1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Die Todo-Liste steht jetzt in TODO.md im Repo (Ambermoon-Advanced, Branch episode4). Die Punkte dieses Blatts wurden dorthin übernommen.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/AmbermoonAdvanced.xlsx
+++ b/AmbermoonAdvanced.xlsx
@@ -23516,7 +23516,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="65.42578125" customWidth="1"/>
@@ -23660,6 +23660,62 @@
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>474</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103: Ausgang Süd / South Exit (Dor Grestin) – war 67 (doppelt mit Ausgang im Weinkeller)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">104: Ausgang Nord / North Exit (Dor Grestin) – war 68 (doppelt mit Training im Weinkeller)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105: Das Nest / The Nest (Dor Grestin) – war 69 (doppelt mit Gildenhändler im Weinkeller)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106: Lebensmittel / Foodstuffs (Dor Grestin) – war 70 (doppelt mit Stadthaus 1 in Spannenberg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hinweise (14.10.2026):</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Dor Grestin: Die 4 Goto-Points oben nutzten schon im Original die Bits 67-70 doppelt (Ambermoon #99). Das Original nutzt jetzt 79-82, die in Advanced belegt sind, daher hier 103-106.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- 17: Der neue Spannenberg-Goto bei (17,23) "Parkverwaltung / Gardening Shed" nutzte fälschlich Bit 16 (wie Stadtgarten O) und nutzt jetzt 17.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- 101/102: In den Daten hat "Weiser / Wise Man" (S'Angrila) Bit 101. Ein Versteck-Goto existiert noch nicht. Frei sind 0 und 102, ab 107 ist alles frei.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/AmbermoonAdvanced.xlsx
+++ b/AmbermoonAdvanced.xlsx
@@ -23538,8 +23538,10 @@
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>450</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17: Parkverwaltung / Gardening Shed (Spannenberg)</t>
+        </is>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
@@ -23653,13 +23655,17 @@
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>473</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101: Weiser / Wise Man (S’Angrila)</t>
+        </is>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>474</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102: Versteck / Hideout (S’Angrila) – vor dem Dunklen Haus (27,24)</t>
+        </is>
       </c>
     </row>
     <row r="31" spans="1:1">
@@ -23707,14 +23713,14 @@
     <row r="38" spans="1:1">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">- 17: Der neue Spannenberg-Goto bei (17,23) "Parkverwaltung / Gardening Shed" nutzte fälschlich Bit 16 (wie Stadtgarten O) und nutzt jetzt 17.</t>
+          <t xml:space="preserve">- 17: Parkverwaltung / Gardening Shed (Spannenberg, bei (17,23)) nutzte fälschlich Bit 16 (wie Stadtgarten O) und nutzt jetzt 17.</t>
         </is>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">- 101/102: In den Daten hat "Weiser / Wise Man" (S'Angrila) Bit 101. Ein Versteck-Goto existiert noch nicht. Frei sind 0 und 102, ab 107 ist alles frei.</t>
+          <t xml:space="preserve">- 101/102: Der Weise hatte in den Daten schon 101 statt wie geplant 102. Das Versteck hat jetzt 102. Bit 0 ist wie im Original unbenutzt, ab 107 ist alles frei.</t>
         </is>
       </c>
     </row>

--- a/AmbermoonAdvanced.xlsx
+++ b/AmbermoonAdvanced.xlsx
@@ -23540,7 +23540,7 @@
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">17: Parkverwaltung / Gardening Shed (Spannenberg)</t>
+          <t xml:space="preserve">17: Gärtnerei / Gardening Shed (Spannenberg)</t>
         </is>
       </c>
     </row>
@@ -23664,7 +23664,7 @@
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">102: Versteck / Hideout (S’Angrila) – vor dem Dunklen Haus (27,24)</t>
+          <t xml:space="preserve">102: Dunkles Haus / Dark House (S’Angrila) – Eingang zum Versteck, (27,24)</t>
         </is>
       </c>
     </row>
@@ -23713,14 +23713,14 @@
     <row r="38" spans="1:1">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">- 17: Parkverwaltung / Gardening Shed (Spannenberg, bei (17,23)) nutzte fälschlich Bit 16 (wie Stadtgarten O) und nutzt jetzt 17.</t>
+          <t xml:space="preserve">- 17: Gärtnerei / Gardening Shed (Spannenberg, bei (17,23)) nutzte fälschlich Bit 16 (wie Stadtgarten O) und nutzt jetzt 17. In der Binärdatei stand noch der alte Name Parkverwaltung.</t>
         </is>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">- 101/102: Der Weise hatte in den Daten schon 101 statt wie geplant 102. Das Versteck hat jetzt 102. Bit 0 ist wie im Original unbenutzt, ab 107 ist alles frei.</t>
+          <t xml:space="preserve">- 101/102: Der Weise hatte in den Daten schon 101 statt wie geplant 102. Das Versteck hat jetzt 102 (Name im Spiel: Dunkles Haus, um nicht zu spoilern). Bit 0 ist wie im Original unbenutzt, ab 107 ist alles frei.</t>
         </is>
       </c>
     </row>

--- a/AmbermoonAdvanced.xlsx
+++ b/AmbermoonAdvanced.xlsx
@@ -9955,7 +9955,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
@@ -10145,6 +10145,23 @@
         <v>1099</v>
       </c>
     </row>
+    <row r="13">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mine Dor Kiredon (345)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chest object (texture 164, like labdata 37) as block 61</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -10157,7 +10174,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.5703125" customWidth="1"/>
@@ -10453,6 +10470,74 @@
         <v>1125</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">343</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dor Kiredon</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chain 20 at (16,21) and (16,23): if Bore (18) is in the party, text 21, he leaves the party (chests 307/308), is hidden in Gemstone, the mine NPC and the chests appear, var 471 is set</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">345</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mine</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NPC Bore (80) at (12,7), chests 307/308 at (11,7) and (10,8) (only active with var 471, block 61 is placed by map 343)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">406</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gemstone Ruinen</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Party member Bore (18) at the position of NPC Bore, initially hidden</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">436</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F-Schiff: Waldmond</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">When leaving the forest moon (var 320), NPC Bore is hidden and party member Bore is shown in Gemstone</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -10461,7 +10546,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -10780,6 +10865,50 @@
       </c>
       <c r="N22" t="s">
         <v>1180</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bore</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mine (345)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bore after he left the party in Dor Kiredon. First talk gives 5000 EXP, trades amber chunks for navstones</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bore</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gemstone Ruinen (406)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Now level 30. Hidden when leaving the forest moon (airship 436), replaced by party member 18</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -10793,7 +10922,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:H122"/>
+  <dimension ref="A1:H124"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="16" customWidth="1"/>
@@ -12263,6 +12392,40 @@
       </c>
       <c r="C122" t="s">
         <v>1407</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">307 (X051)</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mine Dor Kiredon (345)</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bore's equipment (filled by the remove party member event)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">308 (X052)</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mine Dor Kiredon (345)</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bore's items (filled by the remove party member event)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -12865,7 +13028,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -13688,6 +13851,18 @@
       <c r="K27" s="32">
         <f>G7</f>
         <v>155</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bore</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New party member 18: dwarf warrior level 30, 480 LP, 7 APR, helmet, war hammer, chain mail, dwarf shield, leather boots</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -21895,7 +22070,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D253"/>
+  <dimension ref="A1:D255"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="63.42578125" customWidth="1"/>
@@ -23178,6 +23353,20 @@
     <row r="253" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>384</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">471: Bore left the party in Dor Kiredon and works in the mine (shows his 2 chests)</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">472: Bore in the mine thanked the party (5000 EXP given)</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/AmbermoonAdvanced.xlsx
+++ b/AmbermoonAdvanced.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Robert\source\repos\Ambermoon-Advanced\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01BE5FD5-D483-4664-8918-50ADC3B5FF44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7A6C58-8889-41D9-9BA5-C3AB2CE4F5CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="6" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="36" activeTab="42" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Neue Daten Ep3" sheetId="1" r:id="rId1"/>
@@ -55,6 +55,7 @@
     <sheet name="CombatBackgrounds" sheetId="40" r:id="rId40"/>
     <sheet name="ElementChanges" sheetId="41" r:id="rId41"/>
     <sheet name="Shards" sheetId="42" r:id="rId42"/>
+    <sheet name="Music" sheetId="43" r:id="rId43"/>
   </sheets>
   <calcPr calcId="191029" iterate="1" iterateDelta="1E-4"/>
   <extLst>
@@ -77,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3101" uniqueCount="2217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3176" uniqueCount="2285">
   <si>
     <t>Map texts</t>
   </si>
@@ -6845,6 +6846,210 @@
   </si>
   <si>
     <t>Flag 12 (no travel music) set, map music 2 (Mellow Camel Funk)</t>
+  </si>
+  <si>
+    <t>Original usage</t>
+  </si>
+  <si>
+    <t>Advanced usage</t>
+  </si>
+  <si>
+    <t>Who Said Hi Ho</t>
+  </si>
+  <si>
+    <t>Gnome mine</t>
+  </si>
+  <si>
+    <t>Mellow Camel Funk</t>
+  </si>
+  <si>
+    <t>Morag places and sand lizard (riding)</t>
+  </si>
+  <si>
+    <t>Morag world maps 513-528 (map flag 12: no travel music)</t>
+  </si>
+  <si>
+    <t>Close To The Hedge</t>
+  </si>
+  <si>
+    <t>Dwarfs, forest moon indoor</t>
+  </si>
+  <si>
+    <t>Voice Of The Bagpipe</t>
+  </si>
+  <si>
+    <t>Gemstone</t>
+  </si>
+  <si>
+    <t>Downtown</t>
+  </si>
+  <si>
+    <t>Ship</t>
+  </si>
+  <si>
+    <t>Ship (sailing)</t>
+  </si>
+  <si>
+    <t>Whole Lotta Dove</t>
+  </si>
+  <si>
+    <t>Eagle (flying)</t>
+  </si>
+  <si>
+    <t>Horse Is No Disgrace</t>
+  </si>
+  <si>
+    <t>Horse (riding)</t>
+  </si>
+  <si>
+    <t>Don't Look Bach</t>
+  </si>
+  <si>
+    <t>Taverns</t>
+  </si>
+  <si>
+    <t>Rough Waterfront Tavern</t>
+  </si>
+  <si>
+    <t>Sapphire Fireballs Of Pure Love</t>
+  </si>
+  <si>
+    <t>Battle theme</t>
+  </si>
+  <si>
+    <t>The Aum Remains The Same</t>
+  </si>
+  <si>
+    <t>Temple of life</t>
+  </si>
+  <si>
+    <t>Capital</t>
+  </si>
+  <si>
+    <t>Newlake</t>
+  </si>
+  <si>
+    <t>Plodding Along</t>
+  </si>
+  <si>
+    <t>All world maps</t>
+  </si>
+  <si>
+    <t>Compact Disc</t>
+  </si>
+  <si>
+    <t>Magical fly disc</t>
+  </si>
+  <si>
+    <t>Riverside Travelling Blues</t>
+  </si>
+  <si>
+    <t>Nobodys Vault But Mine</t>
+  </si>
+  <si>
+    <t>Thief guild</t>
+  </si>
+  <si>
+    <t>La Crypta Strangiato</t>
+  </si>
+  <si>
+    <t>Grandfather's cellar</t>
+  </si>
+  <si>
+    <t>Misty Dungeon Hop</t>
+  </si>
+  <si>
+    <t>Alchemist tower</t>
+  </si>
+  <si>
+    <t>Burn Baby Burn</t>
+  </si>
+  <si>
+    <t>Witch's broom, Nera's house</t>
+  </si>
+  <si>
+    <t>Bar Brawlin</t>
+  </si>
+  <si>
+    <t>Camp, Inn</t>
+  </si>
+  <si>
+    <t>Psychedelic Dune Groove</t>
+  </si>
+  <si>
+    <t>Sand ship</t>
+  </si>
+  <si>
+    <t>Base of song 33</t>
+  </si>
+  <si>
+    <t>Stairway To Level 50</t>
+  </si>
+  <si>
+    <t>Level up</t>
+  </si>
+  <si>
+    <t>That Hunch Is Back</t>
+  </si>
+  <si>
+    <t>Undeads</t>
+  </si>
+  <si>
+    <t>ChickenSoup</t>
+  </si>
+  <si>
+    <t>Superman mode, Thalion office</t>
+  </si>
+  <si>
+    <t>Dragon Chase In Creepy Dungeon</t>
+  </si>
+  <si>
+    <t>Luminor's tower</t>
+  </si>
+  <si>
+    <t>His Masters Voice</t>
+  </si>
+  <si>
+    <t>Harp, Matthias in Illien</t>
+  </si>
+  <si>
+    <t>No Name</t>
+  </si>
+  <si>
+    <t>House of healers</t>
+  </si>
+  <si>
+    <t>Oh No Not Another Magical Event</t>
+  </si>
+  <si>
+    <t>Magical events (wishing well, pulsing lights, etc)</t>
+  </si>
+  <si>
+    <t>The Uh Oh Song</t>
+  </si>
+  <si>
+    <t>Dramatic events</t>
+  </si>
+  <si>
+    <t>Owner Of A Lonely Sword</t>
+  </si>
+  <si>
+    <t>Grandfather's house</t>
+  </si>
+  <si>
+    <t>Game Over</t>
+  </si>
+  <si>
+    <t>Psychedelic Dune Groove (Temple)</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Council temple (which one: open)</t>
+  </si>
+  <si>
+    <t>New in Advanced. Song 22 starting and looping at position 34, positions 52-53 and the last 3 removed (about 60 s per loop). Source: assets/Temples/music/SONIC.PsychedelicDuneGroove_ab34_cut2. Code: Max_music = 33 in Set_music (the harp still shows 32 songs). Remake support missing.</t>
   </si>
 </sst>
 </file>
@@ -7490,17 +7695,17 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -16888,14 +17093,14 @@
       <c r="B32" s="54" t="s">
         <v>1745</v>
       </c>
-      <c r="C32" s="78" t="s">
+      <c r="C32" s="75" t="s">
         <v>1746</v>
       </c>
-      <c r="D32" s="78"/>
-      <c r="E32" s="78"/>
-      <c r="F32" s="78"/>
-      <c r="G32" s="78"/>
-      <c r="H32" s="78"/>
+      <c r="D32" s="75"/>
+      <c r="E32" s="75"/>
+      <c r="F32" s="75"/>
+      <c r="G32" s="75"/>
+      <c r="H32" s="75"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="36" t="s">
@@ -16904,14 +17109,14 @@
       <c r="B33" s="28" t="s">
         <v>1748</v>
       </c>
-      <c r="C33" s="77" t="s">
+      <c r="C33" s="76" t="s">
         <v>1749</v>
       </c>
-      <c r="D33" s="77"/>
-      <c r="E33" s="77"/>
-      <c r="F33" s="77"/>
-      <c r="G33" s="77"/>
-      <c r="H33" s="77"/>
+      <c r="D33" s="76"/>
+      <c r="E33" s="76"/>
+      <c r="F33" s="76"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="76"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="36" t="s">
@@ -16920,14 +17125,14 @@
       <c r="B34" s="28" t="s">
         <v>1748</v>
       </c>
-      <c r="C34" s="77" t="s">
+      <c r="C34" s="76" t="s">
         <v>1749</v>
       </c>
-      <c r="D34" s="77"/>
-      <c r="E34" s="77"/>
-      <c r="F34" s="77"/>
-      <c r="G34" s="77"/>
-      <c r="H34" s="77"/>
+      <c r="D34" s="76"/>
+      <c r="E34" s="76"/>
+      <c r="F34" s="76"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="76"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="36" t="s">
@@ -16936,14 +17141,14 @@
       <c r="B35" s="28" t="s">
         <v>1748</v>
       </c>
-      <c r="C35" s="77" t="s">
+      <c r="C35" s="76" t="s">
         <v>1749</v>
       </c>
-      <c r="D35" s="77"/>
-      <c r="E35" s="77"/>
-      <c r="F35" s="77"/>
-      <c r="G35" s="77"/>
-      <c r="H35" s="77"/>
+      <c r="D35" s="76"/>
+      <c r="E35" s="76"/>
+      <c r="F35" s="76"/>
+      <c r="G35" s="76"/>
+      <c r="H35" s="76"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="36" t="s">
@@ -16952,14 +17157,14 @@
       <c r="B36" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C36" s="76" t="s">
+      <c r="C36" s="77" t="s">
         <v>1753</v>
       </c>
-      <c r="D36" s="76"/>
-      <c r="E36" s="76"/>
-      <c r="F36" s="76"/>
-      <c r="G36" s="76"/>
-      <c r="H36" s="76"/>
+      <c r="D36" s="77"/>
+      <c r="E36" s="77"/>
+      <c r="F36" s="77"/>
+      <c r="G36" s="77"/>
+      <c r="H36" s="77"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="36" t="s">
@@ -16968,14 +17173,14 @@
       <c r="B37" s="28" t="s">
         <v>1736</v>
       </c>
-      <c r="C37" s="77" t="s">
+      <c r="C37" s="76" t="s">
         <v>1755</v>
       </c>
-      <c r="D37" s="77"/>
-      <c r="E37" s="77"/>
-      <c r="F37" s="77"/>
-      <c r="G37" s="77"/>
-      <c r="H37" s="77"/>
+      <c r="D37" s="76"/>
+      <c r="E37" s="76"/>
+      <c r="F37" s="76"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="76"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="36" t="s">
@@ -16984,14 +17189,14 @@
       <c r="B38" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C38" s="77" t="s">
+      <c r="C38" s="76" t="s">
         <v>1755</v>
       </c>
-      <c r="D38" s="77"/>
-      <c r="E38" s="77"/>
-      <c r="F38" s="77"/>
-      <c r="G38" s="77"/>
-      <c r="H38" s="77"/>
+      <c r="D38" s="76"/>
+      <c r="E38" s="76"/>
+      <c r="F38" s="76"/>
+      <c r="G38" s="76"/>
+      <c r="H38" s="76"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="36" t="s">
@@ -17000,14 +17205,14 @@
       <c r="B39" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C39" s="76" t="s">
+      <c r="C39" s="77" t="s">
         <v>1753</v>
       </c>
-      <c r="D39" s="76"/>
-      <c r="E39" s="76"/>
-      <c r="F39" s="76"/>
-      <c r="G39" s="76"/>
-      <c r="H39" s="76"/>
+      <c r="D39" s="77"/>
+      <c r="E39" s="77"/>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="77"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="36" t="s">
@@ -17016,14 +17221,14 @@
       <c r="B40" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C40" s="76" t="s">
+      <c r="C40" s="77" t="s">
         <v>1753</v>
       </c>
-      <c r="D40" s="76"/>
-      <c r="E40" s="76"/>
-      <c r="F40" s="76"/>
-      <c r="G40" s="76"/>
-      <c r="H40" s="76"/>
+      <c r="D40" s="77"/>
+      <c r="E40" s="77"/>
+      <c r="F40" s="77"/>
+      <c r="G40" s="77"/>
+      <c r="H40" s="77"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="36" t="s">
@@ -17032,14 +17237,14 @@
       <c r="B41" s="28" t="s">
         <v>1737</v>
       </c>
-      <c r="C41" s="76" t="s">
+      <c r="C41" s="77" t="s">
         <v>1759</v>
       </c>
-      <c r="D41" s="76"/>
-      <c r="E41" s="76"/>
-      <c r="F41" s="76"/>
-      <c r="G41" s="76"/>
-      <c r="H41" s="76"/>
+      <c r="D41" s="77"/>
+      <c r="E41" s="77"/>
+      <c r="F41" s="77"/>
+      <c r="G41" s="77"/>
+      <c r="H41" s="77"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="36" t="s">
@@ -17048,14 +17253,14 @@
       <c r="B42" s="28" t="s">
         <v>1738</v>
       </c>
-      <c r="C42" s="76" t="s">
+      <c r="C42" s="77" t="s">
         <v>1761</v>
       </c>
-      <c r="D42" s="76"/>
-      <c r="E42" s="76"/>
-      <c r="F42" s="76"/>
-      <c r="G42" s="76"/>
-      <c r="H42" s="76"/>
+      <c r="D42" s="77"/>
+      <c r="E42" s="77"/>
+      <c r="F42" s="77"/>
+      <c r="G42" s="77"/>
+      <c r="H42" s="77"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="36" t="s">
@@ -17064,14 +17269,14 @@
       <c r="B43" s="28" t="s">
         <v>1739</v>
       </c>
-      <c r="C43" s="76" t="s">
+      <c r="C43" s="77" t="s">
         <v>1763</v>
       </c>
-      <c r="D43" s="76"/>
-      <c r="E43" s="76"/>
-      <c r="F43" s="76"/>
-      <c r="G43" s="76"/>
-      <c r="H43" s="76"/>
+      <c r="D43" s="77"/>
+      <c r="E43" s="77"/>
+      <c r="F43" s="77"/>
+      <c r="G43" s="77"/>
+      <c r="H43" s="77"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="36" t="s">
@@ -17080,26 +17285,26 @@
       <c r="B44" s="28" t="s">
         <v>1740</v>
       </c>
-      <c r="C44" s="76" t="s">
+      <c r="C44" s="77" t="s">
         <v>1765</v>
       </c>
-      <c r="D44" s="76"/>
-      <c r="E44" s="76"/>
-      <c r="F44" s="76"/>
-      <c r="G44" s="76"/>
-      <c r="H44" s="76"/>
+      <c r="D44" s="77"/>
+      <c r="E44" s="77"/>
+      <c r="F44" s="77"/>
+      <c r="G44" s="77"/>
+      <c r="H44" s="77"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="75" t="s">
+      <c r="A48" s="78" t="s">
         <v>1754</v>
       </c>
-      <c r="B48" s="75"/>
-      <c r="C48" s="75"/>
-      <c r="D48" s="75"/>
-      <c r="E48" s="75"/>
-      <c r="F48" s="75"/>
-      <c r="G48" s="75"/>
-      <c r="H48" s="75"/>
+      <c r="B48" s="78"/>
+      <c r="C48" s="78"/>
+      <c r="D48" s="78"/>
+      <c r="E48" s="78"/>
+      <c r="F48" s="78"/>
+      <c r="G48" s="78"/>
+      <c r="H48" s="78"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
@@ -17112,16 +17317,16 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="75" t="s">
+      <c r="A52" s="78" t="s">
         <v>1756</v>
       </c>
-      <c r="B52" s="75"/>
-      <c r="C52" s="75"/>
-      <c r="D52" s="75"/>
-      <c r="E52" s="75"/>
-      <c r="F52" s="75"/>
-      <c r="G52" s="75"/>
-      <c r="H52" s="75"/>
+      <c r="B52" s="78"/>
+      <c r="C52" s="78"/>
+      <c r="D52" s="78"/>
+      <c r="E52" s="78"/>
+      <c r="F52" s="78"/>
+      <c r="G52" s="78"/>
+      <c r="H52" s="78"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -17129,16 +17334,16 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="75" t="s">
+      <c r="A57" s="78" t="s">
         <v>1769</v>
       </c>
-      <c r="B57" s="75"/>
-      <c r="C57" s="75"/>
-      <c r="D57" s="75"/>
-      <c r="E57" s="75"/>
-      <c r="F57" s="75"/>
-      <c r="G57" s="75"/>
-      <c r="H57" s="75"/>
+      <c r="B57" s="78"/>
+      <c r="C57" s="78"/>
+      <c r="D57" s="78"/>
+      <c r="E57" s="78"/>
+      <c r="F57" s="78"/>
+      <c r="G57" s="78"/>
+      <c r="H57" s="78"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
@@ -17206,12 +17411,12 @@
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H73" s="75" t="s">
+      <c r="H73" s="78" t="s">
         <v>1783</v>
       </c>
-      <c r="I73" s="75"/>
-      <c r="J73" s="75"/>
-      <c r="K73" s="75"/>
+      <c r="I73" s="78"/>
+      <c r="J73" s="78"/>
+      <c r="K73" s="78"/>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="55" t="s">
@@ -17778,16 +17983,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="C32:H32"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="C35:H35"/>
-    <mergeCell ref="C36:H36"/>
-    <mergeCell ref="C37:H37"/>
-    <mergeCell ref="C38:H38"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C40:H40"/>
-    <mergeCell ref="C41:H41"/>
     <mergeCell ref="A57:H57"/>
     <mergeCell ref="H73:K73"/>
     <mergeCell ref="C42:H42"/>
@@ -17795,6 +17990,16 @@
     <mergeCell ref="C44:H44"/>
     <mergeCell ref="A48:H48"/>
     <mergeCell ref="A52:H52"/>
+    <mergeCell ref="C37:H37"/>
+    <mergeCell ref="C38:H38"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
+    <mergeCell ref="C41:H41"/>
+    <mergeCell ref="C32:H32"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="C35:H35"/>
+    <mergeCell ref="C36:H36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -17857,13 +18062,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="78" t="s">
         <v>1905</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
@@ -21799,6 +22004,415 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EB917A5-DF3B-4EE0-9368-5DECBA5FA2AE}">
+  <dimension ref="A1:E34"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="255.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="67" t="s">
+        <v>397</v>
+      </c>
+      <c r="B1" s="67" t="s">
+        <v>398</v>
+      </c>
+      <c r="C1" s="67" t="s">
+        <v>2217</v>
+      </c>
+      <c r="D1" s="67" t="s">
+        <v>2218</v>
+      </c>
+      <c r="E1" s="67" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2220</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2221</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2222</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2224</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2226</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2227</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2228</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2229</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>2231</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2233</v>
+      </c>
+      <c r="C9" t="s">
+        <v>2234</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2235</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2236</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>2237</v>
+      </c>
+      <c r="C11" t="s">
+        <v>2236</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2238</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2240</v>
+      </c>
+      <c r="C13" t="s">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>2242</v>
+      </c>
+      <c r="C14" t="s">
+        <v>2243</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>2244</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2246</v>
+      </c>
+      <c r="C16" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>2248</v>
+      </c>
+      <c r="C17" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>2249</v>
+      </c>
+      <c r="C18" t="s">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>2251</v>
+      </c>
+      <c r="C19" t="s">
+        <v>2252</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>2253</v>
+      </c>
+      <c r="C20" t="s">
+        <v>2254</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2255</v>
+      </c>
+      <c r="C21" t="s">
+        <v>2256</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2257</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>2259</v>
+      </c>
+      <c r="C23" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E23" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C24" t="s">
+        <v>2263</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>2264</v>
+      </c>
+      <c r="C25" t="s">
+        <v>2265</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>2266</v>
+      </c>
+      <c r="C26" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>2268</v>
+      </c>
+      <c r="C27" t="s">
+        <v>2269</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>2270</v>
+      </c>
+      <c r="C28" t="s">
+        <v>2271</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>2272</v>
+      </c>
+      <c r="C29" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>2274</v>
+      </c>
+      <c r="C30" t="s">
+        <v>2275</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>2276</v>
+      </c>
+      <c r="C31" t="s">
+        <v>2277</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>2278</v>
+      </c>
+      <c r="C32" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>2280</v>
+      </c>
+      <c r="C33" t="s">
+        <v>2280</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>2281</v>
+      </c>
+      <c r="C34" t="s">
+        <v>2282</v>
+      </c>
+      <c r="D34" t="s">
+        <v>2283</v>
+      </c>
+      <c r="E34" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D255"/>

--- a/AmbermoonAdvanced.xlsx
+++ b/AmbermoonAdvanced.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Robert\source\repos\Ambermoon-Advanced\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7A6C58-8889-41D9-9BA5-C3AB2CE4F5CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{715E6CB1-654C-47A9-B89E-A0331E10411F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="36" activeTab="42" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3176" uniqueCount="2285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3181" uniqueCount="2289">
   <si>
     <t>Map texts</t>
   </si>
@@ -7046,10 +7046,22 @@
     <t>-</t>
   </si>
   <si>
-    <t>Council temple (which one: open)</t>
-  </si>
-  <si>
     <t>New in Advanced. Song 22 starting and looping at position 34, positions 52-53 and the last 3 removed (about 60 s per loop). Source: assets/Temples/music/SONIC.PsychedelicDuneGroove_ab34_cut2. Code: Max_music = 33 in Set_music (the harp still shows 32 songs). Remake support missing.</t>
+  </si>
+  <si>
+    <t>Palast des S'Riel (Prototyp) / Palace of S'Riel (prototype)</t>
+  </si>
+  <si>
+    <t>Temple rework pilot, only reachable with the cheat map jump (t, 487). Built by assets/Temples/tools/build_prototype.py. Labdata 46, palette 59, music 33. Exit to 520 (37,41) like 444. Reuses chests 116/117 of map 444.</t>
+  </si>
+  <si>
+    <t>S'Riel prototype (487): copy of labdata 5 (Gala temple) with floor 20 and ceiling 8. Palette 59 (Sandstein) is new too.</t>
+  </si>
+  <si>
+    <t>Add automaps 485 (27x27, 92 bytes), 486 (11x19, 27 bytes) and 487 (17x17, 37 bytes). They were missing in Save.00, entering 485/486 on the Amiga ends in a fatal error (Init_automap loads the entry for every 3D map).</t>
+  </si>
+  <si>
+    <t>Prototype map 487 (S'Riel); final temple open</t>
   </si>
 </sst>
 </file>
@@ -7674,14 +7686,14 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7695,17 +7707,17 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7918,22 +7930,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="E1" s="69" t="s">
+      <c r="B1" s="68"/>
+      <c r="E1" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="69"/>
-      <c r="I1" s="69" t="s">
+      <c r="F1" s="68"/>
+      <c r="I1" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="69"/>
-      <c r="M1" s="69" t="s">
+      <c r="J1" s="68"/>
+      <c r="M1" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="69"/>
+      <c r="N1" s="68"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2">
@@ -8018,26 +8030,26 @@
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A21" s="69" t="s">
+      <c r="A21" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="69"/>
-      <c r="E21" s="69" t="s">
+      <c r="B21" s="68"/>
+      <c r="E21" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="F21" s="69"/>
-      <c r="I21" s="69" t="s">
+      <c r="F21" s="68"/>
+      <c r="I21" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="69"/>
-      <c r="M21" s="69" t="s">
+      <c r="J21" s="68"/>
+      <c r="M21" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="N21" s="69"/>
-      <c r="Q21" s="69" t="s">
+      <c r="N21" s="68"/>
+      <c r="Q21" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="R21" s="69"/>
+      <c r="R21" s="68"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22">
@@ -9300,7 +9312,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -9936,6 +9948,20 @@
         <v>986</v>
       </c>
     </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>487</v>
+      </c>
+      <c r="B48" t="s">
+        <v>2284</v>
+      </c>
+      <c r="C48" t="s">
+        <v>911</v>
+      </c>
+      <c r="D48" t="s">
+        <v>2285</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -9944,7 +9970,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
@@ -10143,6 +10169,14 @@
       </c>
       <c r="F13" t="s">
         <v>2193</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>46</v>
+      </c>
+      <c r="B14" t="s">
+        <v>2286</v>
       </c>
     </row>
   </sheetData>
@@ -10896,10 +10930,10 @@
       <c r="C1" t="s">
         <v>1100</v>
       </c>
-      <c r="E1" s="68" t="s">
+      <c r="E1" s="70" t="s">
         <v>1101</v>
       </c>
-      <c r="F1" s="68"/>
+      <c r="F1" s="70"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="16">
@@ -11137,10 +11171,10 @@
       <c r="C16" t="s">
         <v>1132</v>
       </c>
-      <c r="E16" s="68" t="s">
+      <c r="E16" s="70" t="s">
         <v>1133</v>
       </c>
-      <c r="F16" s="68"/>
+      <c r="F16" s="70"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="16">
@@ -11220,10 +11254,10 @@
       <c r="C21" t="s">
         <v>1143</v>
       </c>
-      <c r="E21" s="68" t="s">
+      <c r="E21" s="70" t="s">
         <v>1144</v>
       </c>
-      <c r="F21" s="68"/>
+      <c r="F21" s="70"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="16">
@@ -15982,16 +16016,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="70" t="s">
         <v>1617</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="G1" s="68" t="s">
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="G1" s="70" t="s">
         <v>1618</v>
       </c>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -16199,17 +16233,17 @@
       <c r="A1" s="43" t="s">
         <v>1621</v>
       </c>
-      <c r="C1" s="68" t="s">
+      <c r="C1" s="70" t="s">
         <v>1622</v>
       </c>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="G1" s="68" t="s">
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="G1" s="70" t="s">
         <v>1623</v>
       </c>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -17093,14 +17127,14 @@
       <c r="B32" s="54" t="s">
         <v>1745</v>
       </c>
-      <c r="C32" s="75" t="s">
+      <c r="C32" s="78" t="s">
         <v>1746</v>
       </c>
-      <c r="D32" s="75"/>
-      <c r="E32" s="75"/>
-      <c r="F32" s="75"/>
-      <c r="G32" s="75"/>
-      <c r="H32" s="75"/>
+      <c r="D32" s="78"/>
+      <c r="E32" s="78"/>
+      <c r="F32" s="78"/>
+      <c r="G32" s="78"/>
+      <c r="H32" s="78"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="36" t="s">
@@ -17109,14 +17143,14 @@
       <c r="B33" s="28" t="s">
         <v>1748</v>
       </c>
-      <c r="C33" s="76" t="s">
+      <c r="C33" s="77" t="s">
         <v>1749</v>
       </c>
-      <c r="D33" s="76"/>
-      <c r="E33" s="76"/>
-      <c r="F33" s="76"/>
-      <c r="G33" s="76"/>
-      <c r="H33" s="76"/>
+      <c r="D33" s="77"/>
+      <c r="E33" s="77"/>
+      <c r="F33" s="77"/>
+      <c r="G33" s="77"/>
+      <c r="H33" s="77"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="36" t="s">
@@ -17125,14 +17159,14 @@
       <c r="B34" s="28" t="s">
         <v>1748</v>
       </c>
-      <c r="C34" s="76" t="s">
+      <c r="C34" s="77" t="s">
         <v>1749</v>
       </c>
-      <c r="D34" s="76"/>
-      <c r="E34" s="76"/>
-      <c r="F34" s="76"/>
-      <c r="G34" s="76"/>
-      <c r="H34" s="76"/>
+      <c r="D34" s="77"/>
+      <c r="E34" s="77"/>
+      <c r="F34" s="77"/>
+      <c r="G34" s="77"/>
+      <c r="H34" s="77"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="36" t="s">
@@ -17141,14 +17175,14 @@
       <c r="B35" s="28" t="s">
         <v>1748</v>
       </c>
-      <c r="C35" s="76" t="s">
+      <c r="C35" s="77" t="s">
         <v>1749</v>
       </c>
-      <c r="D35" s="76"/>
-      <c r="E35" s="76"/>
-      <c r="F35" s="76"/>
-      <c r="G35" s="76"/>
-      <c r="H35" s="76"/>
+      <c r="D35" s="77"/>
+      <c r="E35" s="77"/>
+      <c r="F35" s="77"/>
+      <c r="G35" s="77"/>
+      <c r="H35" s="77"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="36" t="s">
@@ -17157,14 +17191,14 @@
       <c r="B36" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C36" s="77" t="s">
+      <c r="C36" s="76" t="s">
         <v>1753</v>
       </c>
-      <c r="D36" s="77"/>
-      <c r="E36" s="77"/>
-      <c r="F36" s="77"/>
-      <c r="G36" s="77"/>
-      <c r="H36" s="77"/>
+      <c r="D36" s="76"/>
+      <c r="E36" s="76"/>
+      <c r="F36" s="76"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="76"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="36" t="s">
@@ -17173,14 +17207,14 @@
       <c r="B37" s="28" t="s">
         <v>1736</v>
       </c>
-      <c r="C37" s="76" t="s">
+      <c r="C37" s="77" t="s">
         <v>1755</v>
       </c>
-      <c r="D37" s="76"/>
-      <c r="E37" s="76"/>
-      <c r="F37" s="76"/>
-      <c r="G37" s="76"/>
-      <c r="H37" s="76"/>
+      <c r="D37" s="77"/>
+      <c r="E37" s="77"/>
+      <c r="F37" s="77"/>
+      <c r="G37" s="77"/>
+      <c r="H37" s="77"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="36" t="s">
@@ -17189,14 +17223,14 @@
       <c r="B38" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C38" s="76" t="s">
+      <c r="C38" s="77" t="s">
         <v>1755</v>
       </c>
-      <c r="D38" s="76"/>
-      <c r="E38" s="76"/>
-      <c r="F38" s="76"/>
-      <c r="G38" s="76"/>
-      <c r="H38" s="76"/>
+      <c r="D38" s="77"/>
+      <c r="E38" s="77"/>
+      <c r="F38" s="77"/>
+      <c r="G38" s="77"/>
+      <c r="H38" s="77"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="36" t="s">
@@ -17205,14 +17239,14 @@
       <c r="B39" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C39" s="77" t="s">
+      <c r="C39" s="76" t="s">
         <v>1753</v>
       </c>
-      <c r="D39" s="77"/>
-      <c r="E39" s="77"/>
-      <c r="F39" s="77"/>
-      <c r="G39" s="77"/>
-      <c r="H39" s="77"/>
+      <c r="D39" s="76"/>
+      <c r="E39" s="76"/>
+      <c r="F39" s="76"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="76"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="36" t="s">
@@ -17221,14 +17255,14 @@
       <c r="B40" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C40" s="77" t="s">
+      <c r="C40" s="76" t="s">
         <v>1753</v>
       </c>
-      <c r="D40" s="77"/>
-      <c r="E40" s="77"/>
-      <c r="F40" s="77"/>
-      <c r="G40" s="77"/>
-      <c r="H40" s="77"/>
+      <c r="D40" s="76"/>
+      <c r="E40" s="76"/>
+      <c r="F40" s="76"/>
+      <c r="G40" s="76"/>
+      <c r="H40" s="76"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="36" t="s">
@@ -17237,14 +17271,14 @@
       <c r="B41" s="28" t="s">
         <v>1737</v>
       </c>
-      <c r="C41" s="77" t="s">
+      <c r="C41" s="76" t="s">
         <v>1759</v>
       </c>
-      <c r="D41" s="77"/>
-      <c r="E41" s="77"/>
-      <c r="F41" s="77"/>
-      <c r="G41" s="77"/>
-      <c r="H41" s="77"/>
+      <c r="D41" s="76"/>
+      <c r="E41" s="76"/>
+      <c r="F41" s="76"/>
+      <c r="G41" s="76"/>
+      <c r="H41" s="76"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="36" t="s">
@@ -17253,14 +17287,14 @@
       <c r="B42" s="28" t="s">
         <v>1738</v>
       </c>
-      <c r="C42" s="77" t="s">
+      <c r="C42" s="76" t="s">
         <v>1761</v>
       </c>
-      <c r="D42" s="77"/>
-      <c r="E42" s="77"/>
-      <c r="F42" s="77"/>
-      <c r="G42" s="77"/>
-      <c r="H42" s="77"/>
+      <c r="D42" s="76"/>
+      <c r="E42" s="76"/>
+      <c r="F42" s="76"/>
+      <c r="G42" s="76"/>
+      <c r="H42" s="76"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="36" t="s">
@@ -17269,14 +17303,14 @@
       <c r="B43" s="28" t="s">
         <v>1739</v>
       </c>
-      <c r="C43" s="77" t="s">
+      <c r="C43" s="76" t="s">
         <v>1763</v>
       </c>
-      <c r="D43" s="77"/>
-      <c r="E43" s="77"/>
-      <c r="F43" s="77"/>
-      <c r="G43" s="77"/>
-      <c r="H43" s="77"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="76"/>
+      <c r="F43" s="76"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="76"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="36" t="s">
@@ -17285,26 +17319,26 @@
       <c r="B44" s="28" t="s">
         <v>1740</v>
       </c>
-      <c r="C44" s="77" t="s">
+      <c r="C44" s="76" t="s">
         <v>1765</v>
       </c>
-      <c r="D44" s="77"/>
-      <c r="E44" s="77"/>
-      <c r="F44" s="77"/>
-      <c r="G44" s="77"/>
-      <c r="H44" s="77"/>
+      <c r="D44" s="76"/>
+      <c r="E44" s="76"/>
+      <c r="F44" s="76"/>
+      <c r="G44" s="76"/>
+      <c r="H44" s="76"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="78" t="s">
+      <c r="A48" s="75" t="s">
         <v>1754</v>
       </c>
-      <c r="B48" s="78"/>
-      <c r="C48" s="78"/>
-      <c r="D48" s="78"/>
-      <c r="E48" s="78"/>
-      <c r="F48" s="78"/>
-      <c r="G48" s="78"/>
-      <c r="H48" s="78"/>
+      <c r="B48" s="75"/>
+      <c r="C48" s="75"/>
+      <c r="D48" s="75"/>
+      <c r="E48" s="75"/>
+      <c r="F48" s="75"/>
+      <c r="G48" s="75"/>
+      <c r="H48" s="75"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
@@ -17317,16 +17351,16 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="78" t="s">
+      <c r="A52" s="75" t="s">
         <v>1756</v>
       </c>
-      <c r="B52" s="78"/>
-      <c r="C52" s="78"/>
-      <c r="D52" s="78"/>
-      <c r="E52" s="78"/>
-      <c r="F52" s="78"/>
-      <c r="G52" s="78"/>
-      <c r="H52" s="78"/>
+      <c r="B52" s="75"/>
+      <c r="C52" s="75"/>
+      <c r="D52" s="75"/>
+      <c r="E52" s="75"/>
+      <c r="F52" s="75"/>
+      <c r="G52" s="75"/>
+      <c r="H52" s="75"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -17334,16 +17368,16 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="78" t="s">
+      <c r="A57" s="75" t="s">
         <v>1769</v>
       </c>
-      <c r="B57" s="78"/>
-      <c r="C57" s="78"/>
-      <c r="D57" s="78"/>
-      <c r="E57" s="78"/>
-      <c r="F57" s="78"/>
-      <c r="G57" s="78"/>
-      <c r="H57" s="78"/>
+      <c r="B57" s="75"/>
+      <c r="C57" s="75"/>
+      <c r="D57" s="75"/>
+      <c r="E57" s="75"/>
+      <c r="F57" s="75"/>
+      <c r="G57" s="75"/>
+      <c r="H57" s="75"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
@@ -17411,12 +17445,12 @@
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H73" s="78" t="s">
+      <c r="H73" s="75" t="s">
         <v>1783</v>
       </c>
-      <c r="I73" s="78"/>
-      <c r="J73" s="78"/>
-      <c r="K73" s="78"/>
+      <c r="I73" s="75"/>
+      <c r="J73" s="75"/>
+      <c r="K73" s="75"/>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="55" t="s">
@@ -17983,6 +18017,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="C32:H32"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="C35:H35"/>
+    <mergeCell ref="C36:H36"/>
+    <mergeCell ref="C37:H37"/>
+    <mergeCell ref="C38:H38"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
+    <mergeCell ref="C41:H41"/>
     <mergeCell ref="A57:H57"/>
     <mergeCell ref="H73:K73"/>
     <mergeCell ref="C42:H42"/>
@@ -17990,16 +18034,6 @@
     <mergeCell ref="C44:H44"/>
     <mergeCell ref="A48:H48"/>
     <mergeCell ref="A52:H52"/>
-    <mergeCell ref="C37:H37"/>
-    <mergeCell ref="C38:H38"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C40:H40"/>
-    <mergeCell ref="C41:H41"/>
-    <mergeCell ref="C32:H32"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="C35:H35"/>
-    <mergeCell ref="C36:H36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -18062,13 +18096,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="75" t="s">
         <v>1905</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
@@ -18166,7 +18200,7 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -18217,6 +18251,11 @@
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1922</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>2287</v>
       </c>
     </row>
   </sheetData>
@@ -22402,10 +22441,10 @@
         <v>2282</v>
       </c>
       <c r="D34" t="s">
+        <v>2288</v>
+      </c>
+      <c r="E34" t="s">
         <v>2283</v>
-      </c>
-      <c r="E34" t="s">
-        <v>2284</v>
       </c>
     </row>
   </sheetData>
@@ -22437,10 +22476,10 @@
       <c r="A4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="70" t="s">
+      <c r="C4" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="70"/>
+      <c r="D4" s="69"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -22482,10 +22521,10 @@
       <c r="A11" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="70" t="s">
+      <c r="C11" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="70"/>
+      <c r="D11" s="69"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -24320,11 +24359,11 @@
       <c r="D1" t="s">
         <v>393</v>
       </c>
-      <c r="F1" s="68" t="s">
+      <c r="F1" s="70" t="s">
         <v>400</v>
       </c>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">

--- a/AmbermoonAdvanced.xlsx
+++ b/AmbermoonAdvanced.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Robert\source\repos\Ambermoon-Advanced\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{715E6CB1-654C-47A9-B89E-A0331E10411F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB8A306-860D-4B1E-9782-98590EF10961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="36" activeTab="42" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7046,22 +7046,22 @@
     <t>-</t>
   </si>
   <si>
-    <t>New in Advanced. Song 22 starting and looping at position 34, positions 52-53 and the last 3 removed (about 60 s per loop). Source: assets/Temples/music/SONIC.PsychedelicDuneGroove_ab34_cut2. Code: Max_music = 33 in Set_music (the harp still shows 32 songs). Remake support missing.</t>
-  </si>
-  <si>
     <t>Palast des S'Riel (Prototyp) / Palace of S'Riel (prototype)</t>
   </si>
   <si>
-    <t>Temple rework pilot, only reachable with the cheat map jump (t, 487). Built by assets/Temples/tools/build_prototype.py. Labdata 46, palette 59, music 33. Exit to 520 (37,41) like 444. Reuses chests 116/117 of map 444.</t>
-  </si>
-  <si>
     <t>S'Riel prototype (487): copy of labdata 5 (Gala temple) with floor 20 and ceiling 8. Palette 59 (Sandstein) is new too.</t>
   </si>
   <si>
     <t>Add automaps 485 (27x27, 92 bytes), 486 (11x19, 27 bytes) and 487 (17x17, 37 bytes). They were missing in Save.00, entering 485/486 on the Amiga ends in a fatal error (Init_automap loads the entry for every 3D map).</t>
   </si>
   <si>
-    <t>Prototype map 487 (S'Riel); final temple open</t>
+    <t>Chosen as temple music, not in Music.amb yet</t>
+  </si>
+  <si>
+    <t>New in Advanced. Song 22 starting and looping at position 34, positions 52-53 and the last 3 removed (about 60 s per loop). Source: assets/Temples/music/SONIC.PsychedelicDuneGroove_ab34_cut2. Amiga code ready (Max_music = 33 in Set_music, the harp still shows 32 songs). NOT in Music.amb yet: in the remake Song 33 = Intro, a 33rd Music.amb entry makes the data loading fail. Append it after the remake is changed.</t>
+  </si>
+  <si>
+    <t>Temple rework pilot, only reachable with the cheat map jump (t, 487) or the remake teleport cheat. Built by assets/Temples/tools/build_prototype.py. Labdata 46, palette 59, music 22 (later 33). Exit to 520 (37,41) like 444. Reuses chests 116/117 of map 444.</t>
   </si>
 </sst>
 </file>
@@ -7707,17 +7707,17 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -9953,13 +9953,13 @@
         <v>487</v>
       </c>
       <c r="B48" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="C48" t="s">
         <v>911</v>
       </c>
       <c r="D48" t="s">
-        <v>2285</v>
+        <v>2288</v>
       </c>
     </row>
   </sheetData>
@@ -10176,7 +10176,7 @@
         <v>46</v>
       </c>
       <c r="B14" t="s">
-        <v>2286</v>
+        <v>2284</v>
       </c>
     </row>
   </sheetData>
@@ -17127,14 +17127,14 @@
       <c r="B32" s="54" t="s">
         <v>1745</v>
       </c>
-      <c r="C32" s="78" t="s">
+      <c r="C32" s="75" t="s">
         <v>1746</v>
       </c>
-      <c r="D32" s="78"/>
-      <c r="E32" s="78"/>
-      <c r="F32" s="78"/>
-      <c r="G32" s="78"/>
-      <c r="H32" s="78"/>
+      <c r="D32" s="75"/>
+      <c r="E32" s="75"/>
+      <c r="F32" s="75"/>
+      <c r="G32" s="75"/>
+      <c r="H32" s="75"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="36" t="s">
@@ -17143,14 +17143,14 @@
       <c r="B33" s="28" t="s">
         <v>1748</v>
       </c>
-      <c r="C33" s="77" t="s">
+      <c r="C33" s="76" t="s">
         <v>1749</v>
       </c>
-      <c r="D33" s="77"/>
-      <c r="E33" s="77"/>
-      <c r="F33" s="77"/>
-      <c r="G33" s="77"/>
-      <c r="H33" s="77"/>
+      <c r="D33" s="76"/>
+      <c r="E33" s="76"/>
+      <c r="F33" s="76"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="76"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="36" t="s">
@@ -17159,14 +17159,14 @@
       <c r="B34" s="28" t="s">
         <v>1748</v>
       </c>
-      <c r="C34" s="77" t="s">
+      <c r="C34" s="76" t="s">
         <v>1749</v>
       </c>
-      <c r="D34" s="77"/>
-      <c r="E34" s="77"/>
-      <c r="F34" s="77"/>
-      <c r="G34" s="77"/>
-      <c r="H34" s="77"/>
+      <c r="D34" s="76"/>
+      <c r="E34" s="76"/>
+      <c r="F34" s="76"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="76"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="36" t="s">
@@ -17175,14 +17175,14 @@
       <c r="B35" s="28" t="s">
         <v>1748</v>
       </c>
-      <c r="C35" s="77" t="s">
+      <c r="C35" s="76" t="s">
         <v>1749</v>
       </c>
-      <c r="D35" s="77"/>
-      <c r="E35" s="77"/>
-      <c r="F35" s="77"/>
-      <c r="G35" s="77"/>
-      <c r="H35" s="77"/>
+      <c r="D35" s="76"/>
+      <c r="E35" s="76"/>
+      <c r="F35" s="76"/>
+      <c r="G35" s="76"/>
+      <c r="H35" s="76"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="36" t="s">
@@ -17191,14 +17191,14 @@
       <c r="B36" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C36" s="76" t="s">
+      <c r="C36" s="77" t="s">
         <v>1753</v>
       </c>
-      <c r="D36" s="76"/>
-      <c r="E36" s="76"/>
-      <c r="F36" s="76"/>
-      <c r="G36" s="76"/>
-      <c r="H36" s="76"/>
+      <c r="D36" s="77"/>
+      <c r="E36" s="77"/>
+      <c r="F36" s="77"/>
+      <c r="G36" s="77"/>
+      <c r="H36" s="77"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="36" t="s">
@@ -17207,14 +17207,14 @@
       <c r="B37" s="28" t="s">
         <v>1736</v>
       </c>
-      <c r="C37" s="77" t="s">
+      <c r="C37" s="76" t="s">
         <v>1755</v>
       </c>
-      <c r="D37" s="77"/>
-      <c r="E37" s="77"/>
-      <c r="F37" s="77"/>
-      <c r="G37" s="77"/>
-      <c r="H37" s="77"/>
+      <c r="D37" s="76"/>
+      <c r="E37" s="76"/>
+      <c r="F37" s="76"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="76"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="36" t="s">
@@ -17223,14 +17223,14 @@
       <c r="B38" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C38" s="77" t="s">
+      <c r="C38" s="76" t="s">
         <v>1755</v>
       </c>
-      <c r="D38" s="77"/>
-      <c r="E38" s="77"/>
-      <c r="F38" s="77"/>
-      <c r="G38" s="77"/>
-      <c r="H38" s="77"/>
+      <c r="D38" s="76"/>
+      <c r="E38" s="76"/>
+      <c r="F38" s="76"/>
+      <c r="G38" s="76"/>
+      <c r="H38" s="76"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="36" t="s">
@@ -17239,14 +17239,14 @@
       <c r="B39" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C39" s="76" t="s">
+      <c r="C39" s="77" t="s">
         <v>1753</v>
       </c>
-      <c r="D39" s="76"/>
-      <c r="E39" s="76"/>
-      <c r="F39" s="76"/>
-      <c r="G39" s="76"/>
-      <c r="H39" s="76"/>
+      <c r="D39" s="77"/>
+      <c r="E39" s="77"/>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="77"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="36" t="s">
@@ -17255,14 +17255,14 @@
       <c r="B40" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C40" s="76" t="s">
+      <c r="C40" s="77" t="s">
         <v>1753</v>
       </c>
-      <c r="D40" s="76"/>
-      <c r="E40" s="76"/>
-      <c r="F40" s="76"/>
-      <c r="G40" s="76"/>
-      <c r="H40" s="76"/>
+      <c r="D40" s="77"/>
+      <c r="E40" s="77"/>
+      <c r="F40" s="77"/>
+      <c r="G40" s="77"/>
+      <c r="H40" s="77"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="36" t="s">
@@ -17271,14 +17271,14 @@
       <c r="B41" s="28" t="s">
         <v>1737</v>
       </c>
-      <c r="C41" s="76" t="s">
+      <c r="C41" s="77" t="s">
         <v>1759</v>
       </c>
-      <c r="D41" s="76"/>
-      <c r="E41" s="76"/>
-      <c r="F41" s="76"/>
-      <c r="G41" s="76"/>
-      <c r="H41" s="76"/>
+      <c r="D41" s="77"/>
+      <c r="E41" s="77"/>
+      <c r="F41" s="77"/>
+      <c r="G41" s="77"/>
+      <c r="H41" s="77"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="36" t="s">
@@ -17287,14 +17287,14 @@
       <c r="B42" s="28" t="s">
         <v>1738</v>
       </c>
-      <c r="C42" s="76" t="s">
+      <c r="C42" s="77" t="s">
         <v>1761</v>
       </c>
-      <c r="D42" s="76"/>
-      <c r="E42" s="76"/>
-      <c r="F42" s="76"/>
-      <c r="G42" s="76"/>
-      <c r="H42" s="76"/>
+      <c r="D42" s="77"/>
+      <c r="E42" s="77"/>
+      <c r="F42" s="77"/>
+      <c r="G42" s="77"/>
+      <c r="H42" s="77"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="36" t="s">
@@ -17303,14 +17303,14 @@
       <c r="B43" s="28" t="s">
         <v>1739</v>
       </c>
-      <c r="C43" s="76" t="s">
+      <c r="C43" s="77" t="s">
         <v>1763</v>
       </c>
-      <c r="D43" s="76"/>
-      <c r="E43" s="76"/>
-      <c r="F43" s="76"/>
-      <c r="G43" s="76"/>
-      <c r="H43" s="76"/>
+      <c r="D43" s="77"/>
+      <c r="E43" s="77"/>
+      <c r="F43" s="77"/>
+      <c r="G43" s="77"/>
+      <c r="H43" s="77"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="36" t="s">
@@ -17319,26 +17319,26 @@
       <c r="B44" s="28" t="s">
         <v>1740</v>
       </c>
-      <c r="C44" s="76" t="s">
+      <c r="C44" s="77" t="s">
         <v>1765</v>
       </c>
-      <c r="D44" s="76"/>
-      <c r="E44" s="76"/>
-      <c r="F44" s="76"/>
-      <c r="G44" s="76"/>
-      <c r="H44" s="76"/>
+      <c r="D44" s="77"/>
+      <c r="E44" s="77"/>
+      <c r="F44" s="77"/>
+      <c r="G44" s="77"/>
+      <c r="H44" s="77"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="75" t="s">
+      <c r="A48" s="78" t="s">
         <v>1754</v>
       </c>
-      <c r="B48" s="75"/>
-      <c r="C48" s="75"/>
-      <c r="D48" s="75"/>
-      <c r="E48" s="75"/>
-      <c r="F48" s="75"/>
-      <c r="G48" s="75"/>
-      <c r="H48" s="75"/>
+      <c r="B48" s="78"/>
+      <c r="C48" s="78"/>
+      <c r="D48" s="78"/>
+      <c r="E48" s="78"/>
+      <c r="F48" s="78"/>
+      <c r="G48" s="78"/>
+      <c r="H48" s="78"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
@@ -17351,16 +17351,16 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="75" t="s">
+      <c r="A52" s="78" t="s">
         <v>1756</v>
       </c>
-      <c r="B52" s="75"/>
-      <c r="C52" s="75"/>
-      <c r="D52" s="75"/>
-      <c r="E52" s="75"/>
-      <c r="F52" s="75"/>
-      <c r="G52" s="75"/>
-      <c r="H52" s="75"/>
+      <c r="B52" s="78"/>
+      <c r="C52" s="78"/>
+      <c r="D52" s="78"/>
+      <c r="E52" s="78"/>
+      <c r="F52" s="78"/>
+      <c r="G52" s="78"/>
+      <c r="H52" s="78"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -17368,16 +17368,16 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="75" t="s">
+      <c r="A57" s="78" t="s">
         <v>1769</v>
       </c>
-      <c r="B57" s="75"/>
-      <c r="C57" s="75"/>
-      <c r="D57" s="75"/>
-      <c r="E57" s="75"/>
-      <c r="F57" s="75"/>
-      <c r="G57" s="75"/>
-      <c r="H57" s="75"/>
+      <c r="B57" s="78"/>
+      <c r="C57" s="78"/>
+      <c r="D57" s="78"/>
+      <c r="E57" s="78"/>
+      <c r="F57" s="78"/>
+      <c r="G57" s="78"/>
+      <c r="H57" s="78"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
@@ -17445,12 +17445,12 @@
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H73" s="75" t="s">
+      <c r="H73" s="78" t="s">
         <v>1783</v>
       </c>
-      <c r="I73" s="75"/>
-      <c r="J73" s="75"/>
-      <c r="K73" s="75"/>
+      <c r="I73" s="78"/>
+      <c r="J73" s="78"/>
+      <c r="K73" s="78"/>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="55" t="s">
@@ -18017,16 +18017,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="C32:H32"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="C35:H35"/>
-    <mergeCell ref="C36:H36"/>
-    <mergeCell ref="C37:H37"/>
-    <mergeCell ref="C38:H38"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C40:H40"/>
-    <mergeCell ref="C41:H41"/>
     <mergeCell ref="A57:H57"/>
     <mergeCell ref="H73:K73"/>
     <mergeCell ref="C42:H42"/>
@@ -18034,6 +18024,16 @@
     <mergeCell ref="C44:H44"/>
     <mergeCell ref="A48:H48"/>
     <mergeCell ref="A52:H52"/>
+    <mergeCell ref="C37:H37"/>
+    <mergeCell ref="C38:H38"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
+    <mergeCell ref="C41:H41"/>
+    <mergeCell ref="C32:H32"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="C35:H35"/>
+    <mergeCell ref="C36:H36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -18096,13 +18096,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="78" t="s">
         <v>1905</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
@@ -18255,7 +18255,7 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>2287</v>
+        <v>2285</v>
       </c>
     </row>
   </sheetData>
@@ -22441,10 +22441,10 @@
         <v>2282</v>
       </c>
       <c r="D34" t="s">
-        <v>2288</v>
+        <v>2286</v>
       </c>
       <c r="E34" t="s">
-        <v>2283</v>
+        <v>2287</v>
       </c>
     </row>
   </sheetData>

--- a/AmbermoonAdvanced.xlsx
+++ b/AmbermoonAdvanced.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Robert\source\repos\Ambermoon-Advanced\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB8A306-860D-4B1E-9782-98590EF10961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52AEAF11-B256-4B21-AE61-D4274FE27C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="36" activeTab="42" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3181" uniqueCount="2289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3190" uniqueCount="2293">
   <si>
     <t>Map texts</t>
   </si>
@@ -7049,9 +7049,6 @@
     <t>Palast des S'Riel (Prototyp) / Palace of S'Riel (prototype)</t>
   </si>
   <si>
-    <t>S'Riel prototype (487): copy of labdata 5 (Gala temple) with floor 20 and ceiling 8. Palette 59 (Sandstein) is new too.</t>
-  </si>
-  <si>
     <t>Add automaps 485 (27x27, 92 bytes), 486 (11x19, 27 bytes) and 487 (17x17, 37 bytes). They were missing in Save.00, entering 485/486 on the Amiga ends in a fatal error (Init_automap loads the entry for every 3D map).</t>
   </si>
   <si>
@@ -7062,6 +7059,21 @@
   </si>
   <si>
     <t>Temple rework pilot, only reachable with the cheat map jump (t, 487) or the remake teleport cheat. Built by assets/Temples/tools/build_prototype.py. Labdata 46, palette 59, music 22 (later 33). Exit to 520 (37,41) like 444. Reuses chests 116/117 of map 444.</t>
+  </si>
+  <si>
+    <t>Sandstone wall with friezes and two lotus columns</t>
+  </si>
+  <si>
+    <t>Temple prototype S'Riel (487)</t>
+  </si>
+  <si>
+    <t>Sandstone wall with friezes, no columns (base for window, crest, rosette and painting overlays)</t>
+  </si>
+  <si>
+    <t>Sandstone gateway (dark passage between the columns, passable)</t>
+  </si>
+  <si>
+    <t>S'Riel prototype (487): copy of labdata 5 (Gala temple) with floor 20, ceiling 8 and the new walls 131-138 (sandstone textures 193-195; 134-138 are 194 with the overlays window 72, crest 74, painting 67, rosette 71, painting 68). Palette 59 (Wüstentempel) is new too.</t>
   </si>
 </sst>
 </file>
@@ -7707,17 +7719,17 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -9959,7 +9971,7 @@
         <v>911</v>
       </c>
       <c r="D48" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
     </row>
   </sheetData>
@@ -10176,7 +10188,7 @@
         <v>46</v>
       </c>
       <c r="B14" t="s">
-        <v>2284</v>
+        <v>2292</v>
       </c>
     </row>
   </sheetData>
@@ -14662,7 +14674,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="67.85546875" customWidth="1"/>
@@ -14960,6 +14972,48 @@
         <v>1520</v>
       </c>
       <c r="D21" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>193</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2288</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>194</v>
+      </c>
+      <c r="B23" t="s">
+        <v>2290</v>
+      </c>
+      <c r="C23" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>195</v>
+      </c>
+      <c r="B24" t="s">
+        <v>2291</v>
+      </c>
+      <c r="C24" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D24" t="s">
         <v>1530</v>
       </c>
     </row>
@@ -17127,14 +17181,14 @@
       <c r="B32" s="54" t="s">
         <v>1745</v>
       </c>
-      <c r="C32" s="75" t="s">
+      <c r="C32" s="78" t="s">
         <v>1746</v>
       </c>
-      <c r="D32" s="75"/>
-      <c r="E32" s="75"/>
-      <c r="F32" s="75"/>
-      <c r="G32" s="75"/>
-      <c r="H32" s="75"/>
+      <c r="D32" s="78"/>
+      <c r="E32" s="78"/>
+      <c r="F32" s="78"/>
+      <c r="G32" s="78"/>
+      <c r="H32" s="78"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="36" t="s">
@@ -17143,14 +17197,14 @@
       <c r="B33" s="28" t="s">
         <v>1748</v>
       </c>
-      <c r="C33" s="76" t="s">
+      <c r="C33" s="77" t="s">
         <v>1749</v>
       </c>
-      <c r="D33" s="76"/>
-      <c r="E33" s="76"/>
-      <c r="F33" s="76"/>
-      <c r="G33" s="76"/>
-      <c r="H33" s="76"/>
+      <c r="D33" s="77"/>
+      <c r="E33" s="77"/>
+      <c r="F33" s="77"/>
+      <c r="G33" s="77"/>
+      <c r="H33" s="77"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="36" t="s">
@@ -17159,14 +17213,14 @@
       <c r="B34" s="28" t="s">
         <v>1748</v>
       </c>
-      <c r="C34" s="76" t="s">
+      <c r="C34" s="77" t="s">
         <v>1749</v>
       </c>
-      <c r="D34" s="76"/>
-      <c r="E34" s="76"/>
-      <c r="F34" s="76"/>
-      <c r="G34" s="76"/>
-      <c r="H34" s="76"/>
+      <c r="D34" s="77"/>
+      <c r="E34" s="77"/>
+      <c r="F34" s="77"/>
+      <c r="G34" s="77"/>
+      <c r="H34" s="77"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="36" t="s">
@@ -17175,14 +17229,14 @@
       <c r="B35" s="28" t="s">
         <v>1748</v>
       </c>
-      <c r="C35" s="76" t="s">
+      <c r="C35" s="77" t="s">
         <v>1749</v>
       </c>
-      <c r="D35" s="76"/>
-      <c r="E35" s="76"/>
-      <c r="F35" s="76"/>
-      <c r="G35" s="76"/>
-      <c r="H35" s="76"/>
+      <c r="D35" s="77"/>
+      <c r="E35" s="77"/>
+      <c r="F35" s="77"/>
+      <c r="G35" s="77"/>
+      <c r="H35" s="77"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="36" t="s">
@@ -17191,14 +17245,14 @@
       <c r="B36" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C36" s="77" t="s">
+      <c r="C36" s="76" t="s">
         <v>1753</v>
       </c>
-      <c r="D36" s="77"/>
-      <c r="E36" s="77"/>
-      <c r="F36" s="77"/>
-      <c r="G36" s="77"/>
-      <c r="H36" s="77"/>
+      <c r="D36" s="76"/>
+      <c r="E36" s="76"/>
+      <c r="F36" s="76"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="76"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="36" t="s">
@@ -17207,14 +17261,14 @@
       <c r="B37" s="28" t="s">
         <v>1736</v>
       </c>
-      <c r="C37" s="76" t="s">
+      <c r="C37" s="77" t="s">
         <v>1755</v>
       </c>
-      <c r="D37" s="76"/>
-      <c r="E37" s="76"/>
-      <c r="F37" s="76"/>
-      <c r="G37" s="76"/>
-      <c r="H37" s="76"/>
+      <c r="D37" s="77"/>
+      <c r="E37" s="77"/>
+      <c r="F37" s="77"/>
+      <c r="G37" s="77"/>
+      <c r="H37" s="77"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="36" t="s">
@@ -17223,14 +17277,14 @@
       <c r="B38" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C38" s="76" t="s">
+      <c r="C38" s="77" t="s">
         <v>1755</v>
       </c>
-      <c r="D38" s="76"/>
-      <c r="E38" s="76"/>
-      <c r="F38" s="76"/>
-      <c r="G38" s="76"/>
-      <c r="H38" s="76"/>
+      <c r="D38" s="77"/>
+      <c r="E38" s="77"/>
+      <c r="F38" s="77"/>
+      <c r="G38" s="77"/>
+      <c r="H38" s="77"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="36" t="s">
@@ -17239,14 +17293,14 @@
       <c r="B39" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C39" s="77" t="s">
+      <c r="C39" s="76" t="s">
         <v>1753</v>
       </c>
-      <c r="D39" s="77"/>
-      <c r="E39" s="77"/>
-      <c r="F39" s="77"/>
-      <c r="G39" s="77"/>
-      <c r="H39" s="77"/>
+      <c r="D39" s="76"/>
+      <c r="E39" s="76"/>
+      <c r="F39" s="76"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="76"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="36" t="s">
@@ -17255,14 +17309,14 @@
       <c r="B40" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C40" s="77" t="s">
+      <c r="C40" s="76" t="s">
         <v>1753</v>
       </c>
-      <c r="D40" s="77"/>
-      <c r="E40" s="77"/>
-      <c r="F40" s="77"/>
-      <c r="G40" s="77"/>
-      <c r="H40" s="77"/>
+      <c r="D40" s="76"/>
+      <c r="E40" s="76"/>
+      <c r="F40" s="76"/>
+      <c r="G40" s="76"/>
+      <c r="H40" s="76"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="36" t="s">
@@ -17271,14 +17325,14 @@
       <c r="B41" s="28" t="s">
         <v>1737</v>
       </c>
-      <c r="C41" s="77" t="s">
+      <c r="C41" s="76" t="s">
         <v>1759</v>
       </c>
-      <c r="D41" s="77"/>
-      <c r="E41" s="77"/>
-      <c r="F41" s="77"/>
-      <c r="G41" s="77"/>
-      <c r="H41" s="77"/>
+      <c r="D41" s="76"/>
+      <c r="E41" s="76"/>
+      <c r="F41" s="76"/>
+      <c r="G41" s="76"/>
+      <c r="H41" s="76"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="36" t="s">
@@ -17287,14 +17341,14 @@
       <c r="B42" s="28" t="s">
         <v>1738</v>
       </c>
-      <c r="C42" s="77" t="s">
+      <c r="C42" s="76" t="s">
         <v>1761</v>
       </c>
-      <c r="D42" s="77"/>
-      <c r="E42" s="77"/>
-      <c r="F42" s="77"/>
-      <c r="G42" s="77"/>
-      <c r="H42" s="77"/>
+      <c r="D42" s="76"/>
+      <c r="E42" s="76"/>
+      <c r="F42" s="76"/>
+      <c r="G42" s="76"/>
+      <c r="H42" s="76"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="36" t="s">
@@ -17303,14 +17357,14 @@
       <c r="B43" s="28" t="s">
         <v>1739</v>
       </c>
-      <c r="C43" s="77" t="s">
+      <c r="C43" s="76" t="s">
         <v>1763</v>
       </c>
-      <c r="D43" s="77"/>
-      <c r="E43" s="77"/>
-      <c r="F43" s="77"/>
-      <c r="G43" s="77"/>
-      <c r="H43" s="77"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="76"/>
+      <c r="F43" s="76"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="76"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="36" t="s">
@@ -17319,26 +17373,26 @@
       <c r="B44" s="28" t="s">
         <v>1740</v>
       </c>
-      <c r="C44" s="77" t="s">
+      <c r="C44" s="76" t="s">
         <v>1765</v>
       </c>
-      <c r="D44" s="77"/>
-      <c r="E44" s="77"/>
-      <c r="F44" s="77"/>
-      <c r="G44" s="77"/>
-      <c r="H44" s="77"/>
+      <c r="D44" s="76"/>
+      <c r="E44" s="76"/>
+      <c r="F44" s="76"/>
+      <c r="G44" s="76"/>
+      <c r="H44" s="76"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="78" t="s">
+      <c r="A48" s="75" t="s">
         <v>1754</v>
       </c>
-      <c r="B48" s="78"/>
-      <c r="C48" s="78"/>
-      <c r="D48" s="78"/>
-      <c r="E48" s="78"/>
-      <c r="F48" s="78"/>
-      <c r="G48" s="78"/>
-      <c r="H48" s="78"/>
+      <c r="B48" s="75"/>
+      <c r="C48" s="75"/>
+      <c r="D48" s="75"/>
+      <c r="E48" s="75"/>
+      <c r="F48" s="75"/>
+      <c r="G48" s="75"/>
+      <c r="H48" s="75"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
@@ -17351,16 +17405,16 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="78" t="s">
+      <c r="A52" s="75" t="s">
         <v>1756</v>
       </c>
-      <c r="B52" s="78"/>
-      <c r="C52" s="78"/>
-      <c r="D52" s="78"/>
-      <c r="E52" s="78"/>
-      <c r="F52" s="78"/>
-      <c r="G52" s="78"/>
-      <c r="H52" s="78"/>
+      <c r="B52" s="75"/>
+      <c r="C52" s="75"/>
+      <c r="D52" s="75"/>
+      <c r="E52" s="75"/>
+      <c r="F52" s="75"/>
+      <c r="G52" s="75"/>
+      <c r="H52" s="75"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -17368,16 +17422,16 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="78" t="s">
+      <c r="A57" s="75" t="s">
         <v>1769</v>
       </c>
-      <c r="B57" s="78"/>
-      <c r="C57" s="78"/>
-      <c r="D57" s="78"/>
-      <c r="E57" s="78"/>
-      <c r="F57" s="78"/>
-      <c r="G57" s="78"/>
-      <c r="H57" s="78"/>
+      <c r="B57" s="75"/>
+      <c r="C57" s="75"/>
+      <c r="D57" s="75"/>
+      <c r="E57" s="75"/>
+      <c r="F57" s="75"/>
+      <c r="G57" s="75"/>
+      <c r="H57" s="75"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
@@ -17445,12 +17499,12 @@
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H73" s="78" t="s">
+      <c r="H73" s="75" t="s">
         <v>1783</v>
       </c>
-      <c r="I73" s="78"/>
-      <c r="J73" s="78"/>
-      <c r="K73" s="78"/>
+      <c r="I73" s="75"/>
+      <c r="J73" s="75"/>
+      <c r="K73" s="75"/>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="55" t="s">
@@ -18017,6 +18071,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="C32:H32"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="C35:H35"/>
+    <mergeCell ref="C36:H36"/>
+    <mergeCell ref="C37:H37"/>
+    <mergeCell ref="C38:H38"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
+    <mergeCell ref="C41:H41"/>
     <mergeCell ref="A57:H57"/>
     <mergeCell ref="H73:K73"/>
     <mergeCell ref="C42:H42"/>
@@ -18024,16 +18088,6 @@
     <mergeCell ref="C44:H44"/>
     <mergeCell ref="A48:H48"/>
     <mergeCell ref="A52:H52"/>
-    <mergeCell ref="C37:H37"/>
-    <mergeCell ref="C38:H38"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C40:H40"/>
-    <mergeCell ref="C41:H41"/>
-    <mergeCell ref="C32:H32"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="C35:H35"/>
-    <mergeCell ref="C36:H36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -18096,13 +18150,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="75" t="s">
         <v>1905</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
@@ -18255,7 +18309,7 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>2285</v>
+        <v>2284</v>
       </c>
     </row>
   </sheetData>
@@ -22441,10 +22495,10 @@
         <v>2282</v>
       </c>
       <c r="D34" t="s">
+        <v>2285</v>
+      </c>
+      <c r="E34" t="s">
         <v>2286</v>
-      </c>
-      <c r="E34" t="s">
-        <v>2287</v>
       </c>
     </row>
   </sheetData>

--- a/AmbermoonAdvanced.xlsx
+++ b/AmbermoonAdvanced.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Robert\source\repos\Ambermoon-Advanced\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52AEAF11-B256-4B21-AE61-D4274FE27C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E14F54B-0700-4FE1-A2FA-2CA5868C6A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="36" activeTab="42" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3190" uniqueCount="2293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3181" uniqueCount="2289">
   <si>
     <t>Map texts</t>
   </si>
@@ -7061,19 +7061,7 @@
     <t>Temple rework pilot, only reachable with the cheat map jump (t, 487) or the remake teleport cheat. Built by assets/Temples/tools/build_prototype.py. Labdata 46, palette 59, music 22 (later 33). Exit to 520 (37,41) like 444. Reuses chests 116/117 of map 444.</t>
   </si>
   <si>
-    <t>Sandstone wall with friezes and two lotus columns</t>
-  </si>
-  <si>
-    <t>Temple prototype S'Riel (487)</t>
-  </si>
-  <si>
-    <t>Sandstone wall with friezes, no columns (base for window, crest, rosette and painting overlays)</t>
-  </si>
-  <si>
-    <t>Sandstone gateway (dark passage between the columns, passable)</t>
-  </si>
-  <si>
-    <t>S'Riel prototype (487): copy of labdata 5 (Gala temple) with floor 20, ceiling 8 and the new walls 131-138 (sandstone textures 193-195; 134-138 are 194 with the overlays window 72, crest 74, painting 67, rosette 71, painting 68). Palette 59 (Wüstentempel) is new too.</t>
+    <t>Temple base (first used by the S'Riel prototype, map 487): copy of labdata 5 (Gala temple) with floor 20, ceiling 8, new walls 131-134 (wall 99 with column frames 24/25 and rosette 71 / window 72 / crest 74) and object group 40 (serpent totem, texture 28). With palette 59 'Wüstentempel' (stone colours as sandstone, same index meaning as palette 6) everything turns into sandstone. Details: assets/Temples/Labdata 46.md</t>
   </si>
 </sst>
 </file>
@@ -7719,17 +7707,17 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -10188,7 +10176,7 @@
         <v>46</v>
       </c>
       <c r="B14" t="s">
-        <v>2292</v>
+        <v>2288</v>
       </c>
     </row>
   </sheetData>
@@ -14674,7 +14662,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="67.85546875" customWidth="1"/>
@@ -14972,48 +14960,6 @@
         <v>1520</v>
       </c>
       <c r="D21" t="s">
-        <v>1530</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>193</v>
-      </c>
-      <c r="B22" t="s">
-        <v>2288</v>
-      </c>
-      <c r="C22" t="s">
-        <v>2289</v>
-      </c>
-      <c r="D22" t="s">
-        <v>1530</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>194</v>
-      </c>
-      <c r="B23" t="s">
-        <v>2290</v>
-      </c>
-      <c r="C23" t="s">
-        <v>2289</v>
-      </c>
-      <c r="D23" t="s">
-        <v>1530</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>195</v>
-      </c>
-      <c r="B24" t="s">
-        <v>2291</v>
-      </c>
-      <c r="C24" t="s">
-        <v>2289</v>
-      </c>
-      <c r="D24" t="s">
         <v>1530</v>
       </c>
     </row>
@@ -17181,14 +17127,14 @@
       <c r="B32" s="54" t="s">
         <v>1745</v>
       </c>
-      <c r="C32" s="78" t="s">
+      <c r="C32" s="75" t="s">
         <v>1746</v>
       </c>
-      <c r="D32" s="78"/>
-      <c r="E32" s="78"/>
-      <c r="F32" s="78"/>
-      <c r="G32" s="78"/>
-      <c r="H32" s="78"/>
+      <c r="D32" s="75"/>
+      <c r="E32" s="75"/>
+      <c r="F32" s="75"/>
+      <c r="G32" s="75"/>
+      <c r="H32" s="75"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="36" t="s">
@@ -17197,14 +17143,14 @@
       <c r="B33" s="28" t="s">
         <v>1748</v>
       </c>
-      <c r="C33" s="77" t="s">
+      <c r="C33" s="76" t="s">
         <v>1749</v>
       </c>
-      <c r="D33" s="77"/>
-      <c r="E33" s="77"/>
-      <c r="F33" s="77"/>
-      <c r="G33" s="77"/>
-      <c r="H33" s="77"/>
+      <c r="D33" s="76"/>
+      <c r="E33" s="76"/>
+      <c r="F33" s="76"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="76"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="36" t="s">
@@ -17213,14 +17159,14 @@
       <c r="B34" s="28" t="s">
         <v>1748</v>
       </c>
-      <c r="C34" s="77" t="s">
+      <c r="C34" s="76" t="s">
         <v>1749</v>
       </c>
-      <c r="D34" s="77"/>
-      <c r="E34" s="77"/>
-      <c r="F34" s="77"/>
-      <c r="G34" s="77"/>
-      <c r="H34" s="77"/>
+      <c r="D34" s="76"/>
+      <c r="E34" s="76"/>
+      <c r="F34" s="76"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="76"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="36" t="s">
@@ -17229,14 +17175,14 @@
       <c r="B35" s="28" t="s">
         <v>1748</v>
       </c>
-      <c r="C35" s="77" t="s">
+      <c r="C35" s="76" t="s">
         <v>1749</v>
       </c>
-      <c r="D35" s="77"/>
-      <c r="E35" s="77"/>
-      <c r="F35" s="77"/>
-      <c r="G35" s="77"/>
-      <c r="H35" s="77"/>
+      <c r="D35" s="76"/>
+      <c r="E35" s="76"/>
+      <c r="F35" s="76"/>
+      <c r="G35" s="76"/>
+      <c r="H35" s="76"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="36" t="s">
@@ -17245,14 +17191,14 @@
       <c r="B36" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C36" s="76" t="s">
+      <c r="C36" s="77" t="s">
         <v>1753</v>
       </c>
-      <c r="D36" s="76"/>
-      <c r="E36" s="76"/>
-      <c r="F36" s="76"/>
-      <c r="G36" s="76"/>
-      <c r="H36" s="76"/>
+      <c r="D36" s="77"/>
+      <c r="E36" s="77"/>
+      <c r="F36" s="77"/>
+      <c r="G36" s="77"/>
+      <c r="H36" s="77"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="36" t="s">
@@ -17261,14 +17207,14 @@
       <c r="B37" s="28" t="s">
         <v>1736</v>
       </c>
-      <c r="C37" s="77" t="s">
+      <c r="C37" s="76" t="s">
         <v>1755</v>
       </c>
-      <c r="D37" s="77"/>
-      <c r="E37" s="77"/>
-      <c r="F37" s="77"/>
-      <c r="G37" s="77"/>
-      <c r="H37" s="77"/>
+      <c r="D37" s="76"/>
+      <c r="E37" s="76"/>
+      <c r="F37" s="76"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="76"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="36" t="s">
@@ -17277,14 +17223,14 @@
       <c r="B38" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C38" s="77" t="s">
+      <c r="C38" s="76" t="s">
         <v>1755</v>
       </c>
-      <c r="D38" s="77"/>
-      <c r="E38" s="77"/>
-      <c r="F38" s="77"/>
-      <c r="G38" s="77"/>
-      <c r="H38" s="77"/>
+      <c r="D38" s="76"/>
+      <c r="E38" s="76"/>
+      <c r="F38" s="76"/>
+      <c r="G38" s="76"/>
+      <c r="H38" s="76"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="36" t="s">
@@ -17293,14 +17239,14 @@
       <c r="B39" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C39" s="76" t="s">
+      <c r="C39" s="77" t="s">
         <v>1753</v>
       </c>
-      <c r="D39" s="76"/>
-      <c r="E39" s="76"/>
-      <c r="F39" s="76"/>
-      <c r="G39" s="76"/>
-      <c r="H39" s="76"/>
+      <c r="D39" s="77"/>
+      <c r="E39" s="77"/>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="77"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="36" t="s">
@@ -17309,14 +17255,14 @@
       <c r="B40" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C40" s="76" t="s">
+      <c r="C40" s="77" t="s">
         <v>1753</v>
       </c>
-      <c r="D40" s="76"/>
-      <c r="E40" s="76"/>
-      <c r="F40" s="76"/>
-      <c r="G40" s="76"/>
-      <c r="H40" s="76"/>
+      <c r="D40" s="77"/>
+      <c r="E40" s="77"/>
+      <c r="F40" s="77"/>
+      <c r="G40" s="77"/>
+      <c r="H40" s="77"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="36" t="s">
@@ -17325,14 +17271,14 @@
       <c r="B41" s="28" t="s">
         <v>1737</v>
       </c>
-      <c r="C41" s="76" t="s">
+      <c r="C41" s="77" t="s">
         <v>1759</v>
       </c>
-      <c r="D41" s="76"/>
-      <c r="E41" s="76"/>
-      <c r="F41" s="76"/>
-      <c r="G41" s="76"/>
-      <c r="H41" s="76"/>
+      <c r="D41" s="77"/>
+      <c r="E41" s="77"/>
+      <c r="F41" s="77"/>
+      <c r="G41" s="77"/>
+      <c r="H41" s="77"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="36" t="s">
@@ -17341,14 +17287,14 @@
       <c r="B42" s="28" t="s">
         <v>1738</v>
       </c>
-      <c r="C42" s="76" t="s">
+      <c r="C42" s="77" t="s">
         <v>1761</v>
       </c>
-      <c r="D42" s="76"/>
-      <c r="E42" s="76"/>
-      <c r="F42" s="76"/>
-      <c r="G42" s="76"/>
-      <c r="H42" s="76"/>
+      <c r="D42" s="77"/>
+      <c r="E42" s="77"/>
+      <c r="F42" s="77"/>
+      <c r="G42" s="77"/>
+      <c r="H42" s="77"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="36" t="s">
@@ -17357,14 +17303,14 @@
       <c r="B43" s="28" t="s">
         <v>1739</v>
       </c>
-      <c r="C43" s="76" t="s">
+      <c r="C43" s="77" t="s">
         <v>1763</v>
       </c>
-      <c r="D43" s="76"/>
-      <c r="E43" s="76"/>
-      <c r="F43" s="76"/>
-      <c r="G43" s="76"/>
-      <c r="H43" s="76"/>
+      <c r="D43" s="77"/>
+      <c r="E43" s="77"/>
+      <c r="F43" s="77"/>
+      <c r="G43" s="77"/>
+      <c r="H43" s="77"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="36" t="s">
@@ -17373,26 +17319,26 @@
       <c r="B44" s="28" t="s">
         <v>1740</v>
       </c>
-      <c r="C44" s="76" t="s">
+      <c r="C44" s="77" t="s">
         <v>1765</v>
       </c>
-      <c r="D44" s="76"/>
-      <c r="E44" s="76"/>
-      <c r="F44" s="76"/>
-      <c r="G44" s="76"/>
-      <c r="H44" s="76"/>
+      <c r="D44" s="77"/>
+      <c r="E44" s="77"/>
+      <c r="F44" s="77"/>
+      <c r="G44" s="77"/>
+      <c r="H44" s="77"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="75" t="s">
+      <c r="A48" s="78" t="s">
         <v>1754</v>
       </c>
-      <c r="B48" s="75"/>
-      <c r="C48" s="75"/>
-      <c r="D48" s="75"/>
-      <c r="E48" s="75"/>
-      <c r="F48" s="75"/>
-      <c r="G48" s="75"/>
-      <c r="H48" s="75"/>
+      <c r="B48" s="78"/>
+      <c r="C48" s="78"/>
+      <c r="D48" s="78"/>
+      <c r="E48" s="78"/>
+      <c r="F48" s="78"/>
+      <c r="G48" s="78"/>
+      <c r="H48" s="78"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
@@ -17405,16 +17351,16 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="75" t="s">
+      <c r="A52" s="78" t="s">
         <v>1756</v>
       </c>
-      <c r="B52" s="75"/>
-      <c r="C52" s="75"/>
-      <c r="D52" s="75"/>
-      <c r="E52" s="75"/>
-      <c r="F52" s="75"/>
-      <c r="G52" s="75"/>
-      <c r="H52" s="75"/>
+      <c r="B52" s="78"/>
+      <c r="C52" s="78"/>
+      <c r="D52" s="78"/>
+      <c r="E52" s="78"/>
+      <c r="F52" s="78"/>
+      <c r="G52" s="78"/>
+      <c r="H52" s="78"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -17422,16 +17368,16 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="75" t="s">
+      <c r="A57" s="78" t="s">
         <v>1769</v>
       </c>
-      <c r="B57" s="75"/>
-      <c r="C57" s="75"/>
-      <c r="D57" s="75"/>
-      <c r="E57" s="75"/>
-      <c r="F57" s="75"/>
-      <c r="G57" s="75"/>
-      <c r="H57" s="75"/>
+      <c r="B57" s="78"/>
+      <c r="C57" s="78"/>
+      <c r="D57" s="78"/>
+      <c r="E57" s="78"/>
+      <c r="F57" s="78"/>
+      <c r="G57" s="78"/>
+      <c r="H57" s="78"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
@@ -17499,12 +17445,12 @@
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H73" s="75" t="s">
+      <c r="H73" s="78" t="s">
         <v>1783</v>
       </c>
-      <c r="I73" s="75"/>
-      <c r="J73" s="75"/>
-      <c r="K73" s="75"/>
+      <c r="I73" s="78"/>
+      <c r="J73" s="78"/>
+      <c r="K73" s="78"/>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="55" t="s">
@@ -18071,16 +18017,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="C32:H32"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="C35:H35"/>
-    <mergeCell ref="C36:H36"/>
-    <mergeCell ref="C37:H37"/>
-    <mergeCell ref="C38:H38"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C40:H40"/>
-    <mergeCell ref="C41:H41"/>
     <mergeCell ref="A57:H57"/>
     <mergeCell ref="H73:K73"/>
     <mergeCell ref="C42:H42"/>
@@ -18088,6 +18024,16 @@
     <mergeCell ref="C44:H44"/>
     <mergeCell ref="A48:H48"/>
     <mergeCell ref="A52:H52"/>
+    <mergeCell ref="C37:H37"/>
+    <mergeCell ref="C38:H38"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
+    <mergeCell ref="C41:H41"/>
+    <mergeCell ref="C32:H32"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="C35:H35"/>
+    <mergeCell ref="C36:H36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -18150,13 +18096,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="78" t="s">
         <v>1905</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">

--- a/AmbermoonAdvanced.xlsx
+++ b/AmbermoonAdvanced.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Robert\source\repos\Ambermoon-Advanced\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E14F54B-0700-4FE1-A2FA-2CA5868C6A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B8030B-FB99-4B6A-B152-536B6244491A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="36" activeTab="42" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3181" uniqueCount="2289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3220" uniqueCount="2303">
   <si>
     <t>Map texts</t>
   </si>
@@ -7061,7 +7061,49 @@
     <t>Temple rework pilot, only reachable with the cheat map jump (t, 487) or the remake teleport cheat. Built by assets/Temples/tools/build_prototype.py. Labdata 46, palette 59, music 22 (later 33). Exit to 520 (37,41) like 444. Reuses chests 116/117 of map 444.</t>
   </si>
   <si>
-    <t>Temple base (first used by the S'Riel prototype, map 487): copy of labdata 5 (Gala temple) with floor 20, ceiling 8, new walls 131-134 (wall 99 with column frames 24/25 and rosette 71 / window 72 / crest 74) and object group 40 (serpent totem, texture 28). With palette 59 'Wüstentempel' (stone colours as sandstone, same index meaning as palette 6) everything turns into sandstone. Details: assets/Temples/Labdata 46.md</t>
+    <t>Copy of wall 96 (Prunktür) without the colours 12/13 (replaced by 3/5), for palette 59 where 12/13 are blue-green accents</t>
+  </si>
+  <si>
+    <t>Labdata 46 (temple base)</t>
+  </si>
+  <si>
+    <t>Copy of wall 98 (Doppelbogen) without the colours 12/13 (replaced by 3/5), for palette 59 where 12/13 are blue-green accents</t>
+  </si>
+  <si>
+    <t>Copy of wall 99 (Grundwand) without the colours 12/13 (replaced by 3/5), for palette 59 where 12/13 are blue-green accents</t>
+  </si>
+  <si>
+    <t>Copy of wall 100 (Reliefpfeiler) without the colours 12/13 (replaced by 3/5), for palette 59 where 12/13 are blue-green accents</t>
+  </si>
+  <si>
+    <t>Copy of wall 103 (Relieffries) without the colours 12/13 (replaced by 3/5), for palette 59 where 12/13 are blue-green accents</t>
+  </si>
+  <si>
+    <t>Copy of wall 104 (Dunkles Tor im Relief) without the colours 12/13 (replaced by 3/5), for palette 59 where 12/13 are blue-green accents</t>
+  </si>
+  <si>
+    <t>Copy of wall 125 (Treppe hoch) without the colours 12/13 (replaced by 3/5), for palette 59 where 12/13 are blue-green accents</t>
+  </si>
+  <si>
+    <t>Copy of wall 126 (Treppe runter) without the colours 12/13 (replaced by 3/5), for palette 59 where 12/13 are blue-green accents</t>
+  </si>
+  <si>
+    <t>Copy of overlay 24 (Pillar frame left) without the colours 12/13 (replaced by 3/5)</t>
+  </si>
+  <si>
+    <t>Copy of overlay 25 (Pillar frame right) without the colours 12/13 (replaced by 3/5)</t>
+  </si>
+  <si>
+    <t>Copy of overlay 39 (Stone head) without the colours 12/13 (replaced by 3/5)</t>
+  </si>
+  <si>
+    <t>Copy of overlay 96 (Door pillar frame left) without the colours 12/13 (replaced by 3/5)</t>
+  </si>
+  <si>
+    <t>Copy of overlay 97 (Door pillar frame right) without the colours 12/13 (replaced by 3/5)</t>
+  </si>
+  <si>
+    <t>Temple base (first used by the S'Riel prototype, map 487): copy of labdata 5 (Gala temple) with floor 20, ceiling 8, new walls 131-134 (wall 99 with column frames and rosette / window / crest) and object group 40 (serpent totem). The stone walls and overlays point to copies without the colours 12/13 (walls 193-200, overlays 151-155), so in palette 59 'Wüstentempel' the walls are sandstone and 12/13 are blue-green accents (glass, mosaics, marble, books). Details: assets/Temples/Labdata 46.md</t>
   </si>
 </sst>
 </file>
@@ -7707,17 +7749,17 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -10176,7 +10218,7 @@
         <v>46</v>
       </c>
       <c r="B14" t="s">
-        <v>2288</v>
+        <v>2302</v>
       </c>
     </row>
   </sheetData>
@@ -14662,7 +14704,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="67.85546875" customWidth="1"/>
@@ -14960,6 +15002,118 @@
         <v>1520</v>
       </c>
       <c r="D21" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>193</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2288</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>194</v>
+      </c>
+      <c r="B23" t="s">
+        <v>2290</v>
+      </c>
+      <c r="C23" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>195</v>
+      </c>
+      <c r="B24" t="s">
+        <v>2291</v>
+      </c>
+      <c r="C24" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D24" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>196</v>
+      </c>
+      <c r="B25" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C25" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D25" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>197</v>
+      </c>
+      <c r="B26" t="s">
+        <v>2293</v>
+      </c>
+      <c r="C26" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D26" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>198</v>
+      </c>
+      <c r="B27" t="s">
+        <v>2294</v>
+      </c>
+      <c r="C27" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D27" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>199</v>
+      </c>
+      <c r="B28" t="s">
+        <v>2295</v>
+      </c>
+      <c r="C28" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D28" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>200</v>
+      </c>
+      <c r="B29" t="s">
+        <v>2296</v>
+      </c>
+      <c r="C29" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D29" t="s">
         <v>1530</v>
       </c>
     </row>
@@ -14975,7 +15129,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="43.7109375" customWidth="1"/>
@@ -15824,6 +15978,76 @@
       </c>
       <c r="D60" t="s">
         <v>2143</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>151</v>
+      </c>
+      <c r="B61" t="s">
+        <v>2297</v>
+      </c>
+      <c r="C61" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D61" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>152</v>
+      </c>
+      <c r="B62" t="s">
+        <v>2298</v>
+      </c>
+      <c r="C62" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D62" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>153</v>
+      </c>
+      <c r="B63" t="s">
+        <v>2299</v>
+      </c>
+      <c r="C63" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D63" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>154</v>
+      </c>
+      <c r="B64" t="s">
+        <v>2300</v>
+      </c>
+      <c r="C64" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D64" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>155</v>
+      </c>
+      <c r="B65" t="s">
+        <v>2301</v>
+      </c>
+      <c r="C65" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D65" t="s">
+        <v>1558</v>
       </c>
     </row>
   </sheetData>
@@ -17127,14 +17351,14 @@
       <c r="B32" s="54" t="s">
         <v>1745</v>
       </c>
-      <c r="C32" s="75" t="s">
+      <c r="C32" s="78" t="s">
         <v>1746</v>
       </c>
-      <c r="D32" s="75"/>
-      <c r="E32" s="75"/>
-      <c r="F32" s="75"/>
-      <c r="G32" s="75"/>
-      <c r="H32" s="75"/>
+      <c r="D32" s="78"/>
+      <c r="E32" s="78"/>
+      <c r="F32" s="78"/>
+      <c r="G32" s="78"/>
+      <c r="H32" s="78"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="36" t="s">
@@ -17143,14 +17367,14 @@
       <c r="B33" s="28" t="s">
         <v>1748</v>
       </c>
-      <c r="C33" s="76" t="s">
+      <c r="C33" s="77" t="s">
         <v>1749</v>
       </c>
-      <c r="D33" s="76"/>
-      <c r="E33" s="76"/>
-      <c r="F33" s="76"/>
-      <c r="G33" s="76"/>
-      <c r="H33" s="76"/>
+      <c r="D33" s="77"/>
+      <c r="E33" s="77"/>
+      <c r="F33" s="77"/>
+      <c r="G33" s="77"/>
+      <c r="H33" s="77"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="36" t="s">
@@ -17159,14 +17383,14 @@
       <c r="B34" s="28" t="s">
         <v>1748</v>
       </c>
-      <c r="C34" s="76" t="s">
+      <c r="C34" s="77" t="s">
         <v>1749</v>
       </c>
-      <c r="D34" s="76"/>
-      <c r="E34" s="76"/>
-      <c r="F34" s="76"/>
-      <c r="G34" s="76"/>
-      <c r="H34" s="76"/>
+      <c r="D34" s="77"/>
+      <c r="E34" s="77"/>
+      <c r="F34" s="77"/>
+      <c r="G34" s="77"/>
+      <c r="H34" s="77"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="36" t="s">
@@ -17175,14 +17399,14 @@
       <c r="B35" s="28" t="s">
         <v>1748</v>
       </c>
-      <c r="C35" s="76" t="s">
+      <c r="C35" s="77" t="s">
         <v>1749</v>
       </c>
-      <c r="D35" s="76"/>
-      <c r="E35" s="76"/>
-      <c r="F35" s="76"/>
-      <c r="G35" s="76"/>
-      <c r="H35" s="76"/>
+      <c r="D35" s="77"/>
+      <c r="E35" s="77"/>
+      <c r="F35" s="77"/>
+      <c r="G35" s="77"/>
+      <c r="H35" s="77"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="36" t="s">
@@ -17191,14 +17415,14 @@
       <c r="B36" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C36" s="77" t="s">
+      <c r="C36" s="76" t="s">
         <v>1753</v>
       </c>
-      <c r="D36" s="77"/>
-      <c r="E36" s="77"/>
-      <c r="F36" s="77"/>
-      <c r="G36" s="77"/>
-      <c r="H36" s="77"/>
+      <c r="D36" s="76"/>
+      <c r="E36" s="76"/>
+      <c r="F36" s="76"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="76"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="36" t="s">
@@ -17207,14 +17431,14 @@
       <c r="B37" s="28" t="s">
         <v>1736</v>
       </c>
-      <c r="C37" s="76" t="s">
+      <c r="C37" s="77" t="s">
         <v>1755</v>
       </c>
-      <c r="D37" s="76"/>
-      <c r="E37" s="76"/>
-      <c r="F37" s="76"/>
-      <c r="G37" s="76"/>
-      <c r="H37" s="76"/>
+      <c r="D37" s="77"/>
+      <c r="E37" s="77"/>
+      <c r="F37" s="77"/>
+      <c r="G37" s="77"/>
+      <c r="H37" s="77"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="36" t="s">
@@ -17223,14 +17447,14 @@
       <c r="B38" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C38" s="76" t="s">
+      <c r="C38" s="77" t="s">
         <v>1755</v>
       </c>
-      <c r="D38" s="76"/>
-      <c r="E38" s="76"/>
-      <c r="F38" s="76"/>
-      <c r="G38" s="76"/>
-      <c r="H38" s="76"/>
+      <c r="D38" s="77"/>
+      <c r="E38" s="77"/>
+      <c r="F38" s="77"/>
+      <c r="G38" s="77"/>
+      <c r="H38" s="77"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="36" t="s">
@@ -17239,14 +17463,14 @@
       <c r="B39" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C39" s="77" t="s">
+      <c r="C39" s="76" t="s">
         <v>1753</v>
       </c>
-      <c r="D39" s="77"/>
-      <c r="E39" s="77"/>
-      <c r="F39" s="77"/>
-      <c r="G39" s="77"/>
-      <c r="H39" s="77"/>
+      <c r="D39" s="76"/>
+      <c r="E39" s="76"/>
+      <c r="F39" s="76"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="76"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="36" t="s">
@@ -17255,14 +17479,14 @@
       <c r="B40" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C40" s="77" t="s">
+      <c r="C40" s="76" t="s">
         <v>1753</v>
       </c>
-      <c r="D40" s="77"/>
-      <c r="E40" s="77"/>
-      <c r="F40" s="77"/>
-      <c r="G40" s="77"/>
-      <c r="H40" s="77"/>
+      <c r="D40" s="76"/>
+      <c r="E40" s="76"/>
+      <c r="F40" s="76"/>
+      <c r="G40" s="76"/>
+      <c r="H40" s="76"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="36" t="s">
@@ -17271,14 +17495,14 @@
       <c r="B41" s="28" t="s">
         <v>1737</v>
       </c>
-      <c r="C41" s="77" t="s">
+      <c r="C41" s="76" t="s">
         <v>1759</v>
       </c>
-      <c r="D41" s="77"/>
-      <c r="E41" s="77"/>
-      <c r="F41" s="77"/>
-      <c r="G41" s="77"/>
-      <c r="H41" s="77"/>
+      <c r="D41" s="76"/>
+      <c r="E41" s="76"/>
+      <c r="F41" s="76"/>
+      <c r="G41" s="76"/>
+      <c r="H41" s="76"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="36" t="s">
@@ -17287,14 +17511,14 @@
       <c r="B42" s="28" t="s">
         <v>1738</v>
       </c>
-      <c r="C42" s="77" t="s">
+      <c r="C42" s="76" t="s">
         <v>1761</v>
       </c>
-      <c r="D42" s="77"/>
-      <c r="E42" s="77"/>
-      <c r="F42" s="77"/>
-      <c r="G42" s="77"/>
-      <c r="H42" s="77"/>
+      <c r="D42" s="76"/>
+      <c r="E42" s="76"/>
+      <c r="F42" s="76"/>
+      <c r="G42" s="76"/>
+      <c r="H42" s="76"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="36" t="s">
@@ -17303,14 +17527,14 @@
       <c r="B43" s="28" t="s">
         <v>1739</v>
       </c>
-      <c r="C43" s="77" t="s">
+      <c r="C43" s="76" t="s">
         <v>1763</v>
       </c>
-      <c r="D43" s="77"/>
-      <c r="E43" s="77"/>
-      <c r="F43" s="77"/>
-      <c r="G43" s="77"/>
-      <c r="H43" s="77"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="76"/>
+      <c r="F43" s="76"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="76"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="36" t="s">
@@ -17319,26 +17543,26 @@
       <c r="B44" s="28" t="s">
         <v>1740</v>
       </c>
-      <c r="C44" s="77" t="s">
+      <c r="C44" s="76" t="s">
         <v>1765</v>
       </c>
-      <c r="D44" s="77"/>
-      <c r="E44" s="77"/>
-      <c r="F44" s="77"/>
-      <c r="G44" s="77"/>
-      <c r="H44" s="77"/>
+      <c r="D44" s="76"/>
+      <c r="E44" s="76"/>
+      <c r="F44" s="76"/>
+      <c r="G44" s="76"/>
+      <c r="H44" s="76"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="78" t="s">
+      <c r="A48" s="75" t="s">
         <v>1754</v>
       </c>
-      <c r="B48" s="78"/>
-      <c r="C48" s="78"/>
-      <c r="D48" s="78"/>
-      <c r="E48" s="78"/>
-      <c r="F48" s="78"/>
-      <c r="G48" s="78"/>
-      <c r="H48" s="78"/>
+      <c r="B48" s="75"/>
+      <c r="C48" s="75"/>
+      <c r="D48" s="75"/>
+      <c r="E48" s="75"/>
+      <c r="F48" s="75"/>
+      <c r="G48" s="75"/>
+      <c r="H48" s="75"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
@@ -17351,16 +17575,16 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="78" t="s">
+      <c r="A52" s="75" t="s">
         <v>1756</v>
       </c>
-      <c r="B52" s="78"/>
-      <c r="C52" s="78"/>
-      <c r="D52" s="78"/>
-      <c r="E52" s="78"/>
-      <c r="F52" s="78"/>
-      <c r="G52" s="78"/>
-      <c r="H52" s="78"/>
+      <c r="B52" s="75"/>
+      <c r="C52" s="75"/>
+      <c r="D52" s="75"/>
+      <c r="E52" s="75"/>
+      <c r="F52" s="75"/>
+      <c r="G52" s="75"/>
+      <c r="H52" s="75"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -17368,16 +17592,16 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="78" t="s">
+      <c r="A57" s="75" t="s">
         <v>1769</v>
       </c>
-      <c r="B57" s="78"/>
-      <c r="C57" s="78"/>
-      <c r="D57" s="78"/>
-      <c r="E57" s="78"/>
-      <c r="F57" s="78"/>
-      <c r="G57" s="78"/>
-      <c r="H57" s="78"/>
+      <c r="B57" s="75"/>
+      <c r="C57" s="75"/>
+      <c r="D57" s="75"/>
+      <c r="E57" s="75"/>
+      <c r="F57" s="75"/>
+      <c r="G57" s="75"/>
+      <c r="H57" s="75"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
@@ -17445,12 +17669,12 @@
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H73" s="78" t="s">
+      <c r="H73" s="75" t="s">
         <v>1783</v>
       </c>
-      <c r="I73" s="78"/>
-      <c r="J73" s="78"/>
-      <c r="K73" s="78"/>
+      <c r="I73" s="75"/>
+      <c r="J73" s="75"/>
+      <c r="K73" s="75"/>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="55" t="s">
@@ -18017,6 +18241,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="C32:H32"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="C35:H35"/>
+    <mergeCell ref="C36:H36"/>
+    <mergeCell ref="C37:H37"/>
+    <mergeCell ref="C38:H38"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
+    <mergeCell ref="C41:H41"/>
     <mergeCell ref="A57:H57"/>
     <mergeCell ref="H73:K73"/>
     <mergeCell ref="C42:H42"/>
@@ -18024,16 +18258,6 @@
     <mergeCell ref="C44:H44"/>
     <mergeCell ref="A48:H48"/>
     <mergeCell ref="A52:H52"/>
-    <mergeCell ref="C37:H37"/>
-    <mergeCell ref="C38:H38"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C40:H40"/>
-    <mergeCell ref="C41:H41"/>
-    <mergeCell ref="C32:H32"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="C35:H35"/>
-    <mergeCell ref="C36:H36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -18096,13 +18320,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="75" t="s">
         <v>1905</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">

--- a/AmbermoonAdvanced.xlsx
+++ b/AmbermoonAdvanced.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Robert\source\repos\Ambermoon-Advanced\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B8030B-FB99-4B6A-B152-536B6244491A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B19C78-2B21-40A6-B758-69FAA40B6061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="36" activeTab="42" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3220" uniqueCount="2303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3223" uniqueCount="2305">
   <si>
     <t>Map texts</t>
   </si>
@@ -7104,6 +7104,12 @@
   </si>
   <si>
     <t>Temple base (first used by the S'Riel prototype, map 487): copy of labdata 5 (Gala temple) with floor 20, ceiling 8, new walls 131-134 (wall 99 with column frames and rosette / window / crest) and object group 40 (serpent totem). The stone walls and overlays point to copies without the colours 12/13 (walls 193-200, overlays 151-155), so in palette 59 'Wüstentempel' the walls are sandstone and 12/13 are blue-green accents (glass, mosaics, marble, books). Details: assets/Temples/Labdata 46.md</t>
+  </si>
+  <si>
+    <t>Palast des S'Orel (Prototyp) / Palace of S'Orel (prototype)</t>
+  </si>
+  <si>
+    <t>Temple rework S'Orel (barracks), only reachable with the cheat map jump (t, 488) or the remake teleport cheat. Built by assets/Temples/tools/build_prototype.py. Labdata 46, palette 60 'Kaserne', music 18, no map. New monster group 172 (6 magic guards). Reuses door 33 (key 388) and chests 118/119 of map 445. Exit to 525 (33,28) like 445.</t>
   </si>
 </sst>
 </file>
@@ -7749,17 +7755,17 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -9354,7 +9360,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -10002,6 +10008,20 @@
       </c>
       <c r="D48" t="s">
         <v>2287</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>488</v>
+      </c>
+      <c r="B49" t="s">
+        <v>2303</v>
+      </c>
+      <c r="C49" t="s">
+        <v>911</v>
+      </c>
+      <c r="D49" t="s">
+        <v>2304</v>
       </c>
     </row>
   </sheetData>
@@ -17351,14 +17371,14 @@
       <c r="B32" s="54" t="s">
         <v>1745</v>
       </c>
-      <c r="C32" s="78" t="s">
+      <c r="C32" s="75" t="s">
         <v>1746</v>
       </c>
-      <c r="D32" s="78"/>
-      <c r="E32" s="78"/>
-      <c r="F32" s="78"/>
-      <c r="G32" s="78"/>
-      <c r="H32" s="78"/>
+      <c r="D32" s="75"/>
+      <c r="E32" s="75"/>
+      <c r="F32" s="75"/>
+      <c r="G32" s="75"/>
+      <c r="H32" s="75"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="36" t="s">
@@ -17367,14 +17387,14 @@
       <c r="B33" s="28" t="s">
         <v>1748</v>
       </c>
-      <c r="C33" s="77" t="s">
+      <c r="C33" s="76" t="s">
         <v>1749</v>
       </c>
-      <c r="D33" s="77"/>
-      <c r="E33" s="77"/>
-      <c r="F33" s="77"/>
-      <c r="G33" s="77"/>
-      <c r="H33" s="77"/>
+      <c r="D33" s="76"/>
+      <c r="E33" s="76"/>
+      <c r="F33" s="76"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="76"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="36" t="s">
@@ -17383,14 +17403,14 @@
       <c r="B34" s="28" t="s">
         <v>1748</v>
       </c>
-      <c r="C34" s="77" t="s">
+      <c r="C34" s="76" t="s">
         <v>1749</v>
       </c>
-      <c r="D34" s="77"/>
-      <c r="E34" s="77"/>
-      <c r="F34" s="77"/>
-      <c r="G34" s="77"/>
-      <c r="H34" s="77"/>
+      <c r="D34" s="76"/>
+      <c r="E34" s="76"/>
+      <c r="F34" s="76"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="76"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="36" t="s">
@@ -17399,14 +17419,14 @@
       <c r="B35" s="28" t="s">
         <v>1748</v>
       </c>
-      <c r="C35" s="77" t="s">
+      <c r="C35" s="76" t="s">
         <v>1749</v>
       </c>
-      <c r="D35" s="77"/>
-      <c r="E35" s="77"/>
-      <c r="F35" s="77"/>
-      <c r="G35" s="77"/>
-      <c r="H35" s="77"/>
+      <c r="D35" s="76"/>
+      <c r="E35" s="76"/>
+      <c r="F35" s="76"/>
+      <c r="G35" s="76"/>
+      <c r="H35" s="76"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="36" t="s">
@@ -17415,14 +17435,14 @@
       <c r="B36" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C36" s="76" t="s">
+      <c r="C36" s="77" t="s">
         <v>1753</v>
       </c>
-      <c r="D36" s="76"/>
-      <c r="E36" s="76"/>
-      <c r="F36" s="76"/>
-      <c r="G36" s="76"/>
-      <c r="H36" s="76"/>
+      <c r="D36" s="77"/>
+      <c r="E36" s="77"/>
+      <c r="F36" s="77"/>
+      <c r="G36" s="77"/>
+      <c r="H36" s="77"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="36" t="s">
@@ -17431,14 +17451,14 @@
       <c r="B37" s="28" t="s">
         <v>1736</v>
       </c>
-      <c r="C37" s="77" t="s">
+      <c r="C37" s="76" t="s">
         <v>1755</v>
       </c>
-      <c r="D37" s="77"/>
-      <c r="E37" s="77"/>
-      <c r="F37" s="77"/>
-      <c r="G37" s="77"/>
-      <c r="H37" s="77"/>
+      <c r="D37" s="76"/>
+      <c r="E37" s="76"/>
+      <c r="F37" s="76"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="76"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="36" t="s">
@@ -17447,14 +17467,14 @@
       <c r="B38" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C38" s="77" t="s">
+      <c r="C38" s="76" t="s">
         <v>1755</v>
       </c>
-      <c r="D38" s="77"/>
-      <c r="E38" s="77"/>
-      <c r="F38" s="77"/>
-      <c r="G38" s="77"/>
-      <c r="H38" s="77"/>
+      <c r="D38" s="76"/>
+      <c r="E38" s="76"/>
+      <c r="F38" s="76"/>
+      <c r="G38" s="76"/>
+      <c r="H38" s="76"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="36" t="s">
@@ -17463,14 +17483,14 @@
       <c r="B39" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C39" s="76" t="s">
+      <c r="C39" s="77" t="s">
         <v>1753</v>
       </c>
-      <c r="D39" s="76"/>
-      <c r="E39" s="76"/>
-      <c r="F39" s="76"/>
-      <c r="G39" s="76"/>
-      <c r="H39" s="76"/>
+      <c r="D39" s="77"/>
+      <c r="E39" s="77"/>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="77"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="36" t="s">
@@ -17479,14 +17499,14 @@
       <c r="B40" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C40" s="76" t="s">
+      <c r="C40" s="77" t="s">
         <v>1753</v>
       </c>
-      <c r="D40" s="76"/>
-      <c r="E40" s="76"/>
-      <c r="F40" s="76"/>
-      <c r="G40" s="76"/>
-      <c r="H40" s="76"/>
+      <c r="D40" s="77"/>
+      <c r="E40" s="77"/>
+      <c r="F40" s="77"/>
+      <c r="G40" s="77"/>
+      <c r="H40" s="77"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="36" t="s">
@@ -17495,14 +17515,14 @@
       <c r="B41" s="28" t="s">
         <v>1737</v>
       </c>
-      <c r="C41" s="76" t="s">
+      <c r="C41" s="77" t="s">
         <v>1759</v>
       </c>
-      <c r="D41" s="76"/>
-      <c r="E41" s="76"/>
-      <c r="F41" s="76"/>
-      <c r="G41" s="76"/>
-      <c r="H41" s="76"/>
+      <c r="D41" s="77"/>
+      <c r="E41" s="77"/>
+      <c r="F41" s="77"/>
+      <c r="G41" s="77"/>
+      <c r="H41" s="77"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="36" t="s">
@@ -17511,14 +17531,14 @@
       <c r="B42" s="28" t="s">
         <v>1738</v>
       </c>
-      <c r="C42" s="76" t="s">
+      <c r="C42" s="77" t="s">
         <v>1761</v>
       </c>
-      <c r="D42" s="76"/>
-      <c r="E42" s="76"/>
-      <c r="F42" s="76"/>
-      <c r="G42" s="76"/>
-      <c r="H42" s="76"/>
+      <c r="D42" s="77"/>
+      <c r="E42" s="77"/>
+      <c r="F42" s="77"/>
+      <c r="G42" s="77"/>
+      <c r="H42" s="77"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="36" t="s">
@@ -17527,14 +17547,14 @@
       <c r="B43" s="28" t="s">
         <v>1739</v>
       </c>
-      <c r="C43" s="76" t="s">
+      <c r="C43" s="77" t="s">
         <v>1763</v>
       </c>
-      <c r="D43" s="76"/>
-      <c r="E43" s="76"/>
-      <c r="F43" s="76"/>
-      <c r="G43" s="76"/>
-      <c r="H43" s="76"/>
+      <c r="D43" s="77"/>
+      <c r="E43" s="77"/>
+      <c r="F43" s="77"/>
+      <c r="G43" s="77"/>
+      <c r="H43" s="77"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="36" t="s">
@@ -17543,26 +17563,26 @@
       <c r="B44" s="28" t="s">
         <v>1740</v>
       </c>
-      <c r="C44" s="76" t="s">
+      <c r="C44" s="77" t="s">
         <v>1765</v>
       </c>
-      <c r="D44" s="76"/>
-      <c r="E44" s="76"/>
-      <c r="F44" s="76"/>
-      <c r="G44" s="76"/>
-      <c r="H44" s="76"/>
+      <c r="D44" s="77"/>
+      <c r="E44" s="77"/>
+      <c r="F44" s="77"/>
+      <c r="G44" s="77"/>
+      <c r="H44" s="77"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="75" t="s">
+      <c r="A48" s="78" t="s">
         <v>1754</v>
       </c>
-      <c r="B48" s="75"/>
-      <c r="C48" s="75"/>
-      <c r="D48" s="75"/>
-      <c r="E48" s="75"/>
-      <c r="F48" s="75"/>
-      <c r="G48" s="75"/>
-      <c r="H48" s="75"/>
+      <c r="B48" s="78"/>
+      <c r="C48" s="78"/>
+      <c r="D48" s="78"/>
+      <c r="E48" s="78"/>
+      <c r="F48" s="78"/>
+      <c r="G48" s="78"/>
+      <c r="H48" s="78"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
@@ -17575,16 +17595,16 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="75" t="s">
+      <c r="A52" s="78" t="s">
         <v>1756</v>
       </c>
-      <c r="B52" s="75"/>
-      <c r="C52" s="75"/>
-      <c r="D52" s="75"/>
-      <c r="E52" s="75"/>
-      <c r="F52" s="75"/>
-      <c r="G52" s="75"/>
-      <c r="H52" s="75"/>
+      <c r="B52" s="78"/>
+      <c r="C52" s="78"/>
+      <c r="D52" s="78"/>
+      <c r="E52" s="78"/>
+      <c r="F52" s="78"/>
+      <c r="G52" s="78"/>
+      <c r="H52" s="78"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -17592,16 +17612,16 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="75" t="s">
+      <c r="A57" s="78" t="s">
         <v>1769</v>
       </c>
-      <c r="B57" s="75"/>
-      <c r="C57" s="75"/>
-      <c r="D57" s="75"/>
-      <c r="E57" s="75"/>
-      <c r="F57" s="75"/>
-      <c r="G57" s="75"/>
-      <c r="H57" s="75"/>
+      <c r="B57" s="78"/>
+      <c r="C57" s="78"/>
+      <c r="D57" s="78"/>
+      <c r="E57" s="78"/>
+      <c r="F57" s="78"/>
+      <c r="G57" s="78"/>
+      <c r="H57" s="78"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
@@ -17669,12 +17689,12 @@
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H73" s="75" t="s">
+      <c r="H73" s="78" t="s">
         <v>1783</v>
       </c>
-      <c r="I73" s="75"/>
-      <c r="J73" s="75"/>
-      <c r="K73" s="75"/>
+      <c r="I73" s="78"/>
+      <c r="J73" s="78"/>
+      <c r="K73" s="78"/>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="55" t="s">
@@ -18241,16 +18261,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="C32:H32"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="C35:H35"/>
-    <mergeCell ref="C36:H36"/>
-    <mergeCell ref="C37:H37"/>
-    <mergeCell ref="C38:H38"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C40:H40"/>
-    <mergeCell ref="C41:H41"/>
     <mergeCell ref="A57:H57"/>
     <mergeCell ref="H73:K73"/>
     <mergeCell ref="C42:H42"/>
@@ -18258,6 +18268,16 @@
     <mergeCell ref="C44:H44"/>
     <mergeCell ref="A48:H48"/>
     <mergeCell ref="A52:H52"/>
+    <mergeCell ref="C37:H37"/>
+    <mergeCell ref="C38:H38"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
+    <mergeCell ref="C41:H41"/>
+    <mergeCell ref="C32:H32"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="C35:H35"/>
+    <mergeCell ref="C36:H36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -18320,13 +18340,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="78" t="s">
         <v>1905</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">

--- a/AmbermoonAdvanced.xlsx
+++ b/AmbermoonAdvanced.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Robert\source\repos\Ambermoon-Advanced\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B19C78-2B21-40A6-B758-69FAA40B6061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B51921E-0CD2-4DBC-9081-07E7CC7B47CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="36" activeTab="42" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7049,9 +7049,6 @@
     <t>Palast des S'Riel (Prototyp) / Palace of S'Riel (prototype)</t>
   </si>
   <si>
-    <t>Add automaps 485 (27x27, 92 bytes), 486 (11x19, 27 bytes) and 487 (17x17, 37 bytes). They were missing in Save.00, entering 485/486 on the Amiga ends in a fatal error (Init_automap loads the entry for every 3D map).</t>
-  </si>
-  <si>
     <t>Chosen as temple music, not in Music.amb yet</t>
   </si>
   <si>
@@ -7110,6 +7107,9 @@
   </si>
   <si>
     <t>Temple rework S'Orel (barracks), only reachable with the cheat map jump (t, 488) or the remake teleport cheat. Built by assets/Temples/tools/build_prototype.py. Labdata 46, palette 60 'Kaserne', music 18, no map. New monster group 172 (6 magic guards). Reuses door 33 (key 388) and chests 118/119 of map 445. Exit to 525 (33,28) like 445.</t>
+  </si>
+  <si>
+    <t>Add automaps 485 (27x27, 92 bytes), 486 (11x19, 27 bytes), 487 (17x17, 37 bytes) and 488 (21x21, 56 bytes). They were missing in Save.00, entering 485/486 on the Amiga ends in a fatal error (Init_automap loads the entry for every 3D map).</t>
   </si>
 </sst>
 </file>
@@ -7755,17 +7755,17 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -10007,7 +10007,7 @@
         <v>911</v>
       </c>
       <c r="D48" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -10015,13 +10015,13 @@
         <v>488</v>
       </c>
       <c r="B49" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="C49" t="s">
         <v>911</v>
       </c>
       <c r="D49" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
     </row>
   </sheetData>
@@ -10238,7 +10238,7 @@
         <v>46</v>
       </c>
       <c r="B14" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
     </row>
   </sheetData>
@@ -15030,10 +15030,10 @@
         <v>193</v>
       </c>
       <c r="B22" t="s">
+        <v>2287</v>
+      </c>
+      <c r="C22" t="s">
         <v>2288</v>
-      </c>
-      <c r="C22" t="s">
-        <v>2289</v>
       </c>
       <c r="D22" t="s">
         <v>1530</v>
@@ -15044,10 +15044,10 @@
         <v>194</v>
       </c>
       <c r="B23" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="C23" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="D23" t="s">
         <v>1530</v>
@@ -15058,10 +15058,10 @@
         <v>195</v>
       </c>
       <c r="B24" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="C24" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="D24" t="s">
         <v>1530</v>
@@ -15072,10 +15072,10 @@
         <v>196</v>
       </c>
       <c r="B25" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
       <c r="C25" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="D25" t="s">
         <v>1530</v>
@@ -15086,10 +15086,10 @@
         <v>197</v>
       </c>
       <c r="B26" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
       <c r="C26" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="D26" t="s">
         <v>1530</v>
@@ -15100,10 +15100,10 @@
         <v>198</v>
       </c>
       <c r="B27" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="C27" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="D27" t="s">
         <v>1530</v>
@@ -15114,10 +15114,10 @@
         <v>199</v>
       </c>
       <c r="B28" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="C28" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="D28" t="s">
         <v>1530</v>
@@ -15128,10 +15128,10 @@
         <v>200</v>
       </c>
       <c r="B29" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="C29" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="D29" t="s">
         <v>1530</v>
@@ -16005,10 +16005,10 @@
         <v>151</v>
       </c>
       <c r="B61" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="C61" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="D61" t="s">
         <v>1558</v>
@@ -16019,10 +16019,10 @@
         <v>152</v>
       </c>
       <c r="B62" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="C62" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="D62" t="s">
         <v>1558</v>
@@ -16033,10 +16033,10 @@
         <v>153</v>
       </c>
       <c r="B63" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="C63" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="D63" t="s">
         <v>1558</v>
@@ -16047,10 +16047,10 @@
         <v>154</v>
       </c>
       <c r="B64" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="C64" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="D64" t="s">
         <v>1558</v>
@@ -16061,10 +16061,10 @@
         <v>155</v>
       </c>
       <c r="B65" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="C65" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="D65" t="s">
         <v>1558</v>
@@ -17371,14 +17371,14 @@
       <c r="B32" s="54" t="s">
         <v>1745</v>
       </c>
-      <c r="C32" s="75" t="s">
+      <c r="C32" s="78" t="s">
         <v>1746</v>
       </c>
-      <c r="D32" s="75"/>
-      <c r="E32" s="75"/>
-      <c r="F32" s="75"/>
-      <c r="G32" s="75"/>
-      <c r="H32" s="75"/>
+      <c r="D32" s="78"/>
+      <c r="E32" s="78"/>
+      <c r="F32" s="78"/>
+      <c r="G32" s="78"/>
+      <c r="H32" s="78"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="36" t="s">
@@ -17387,14 +17387,14 @@
       <c r="B33" s="28" t="s">
         <v>1748</v>
       </c>
-      <c r="C33" s="76" t="s">
+      <c r="C33" s="77" t="s">
         <v>1749</v>
       </c>
-      <c r="D33" s="76"/>
-      <c r="E33" s="76"/>
-      <c r="F33" s="76"/>
-      <c r="G33" s="76"/>
-      <c r="H33" s="76"/>
+      <c r="D33" s="77"/>
+      <c r="E33" s="77"/>
+      <c r="F33" s="77"/>
+      <c r="G33" s="77"/>
+      <c r="H33" s="77"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="36" t="s">
@@ -17403,14 +17403,14 @@
       <c r="B34" s="28" t="s">
         <v>1748</v>
       </c>
-      <c r="C34" s="76" t="s">
+      <c r="C34" s="77" t="s">
         <v>1749</v>
       </c>
-      <c r="D34" s="76"/>
-      <c r="E34" s="76"/>
-      <c r="F34" s="76"/>
-      <c r="G34" s="76"/>
-      <c r="H34" s="76"/>
+      <c r="D34" s="77"/>
+      <c r="E34" s="77"/>
+      <c r="F34" s="77"/>
+      <c r="G34" s="77"/>
+      <c r="H34" s="77"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="36" t="s">
@@ -17419,14 +17419,14 @@
       <c r="B35" s="28" t="s">
         <v>1748</v>
       </c>
-      <c r="C35" s="76" t="s">
+      <c r="C35" s="77" t="s">
         <v>1749</v>
       </c>
-      <c r="D35" s="76"/>
-      <c r="E35" s="76"/>
-      <c r="F35" s="76"/>
-      <c r="G35" s="76"/>
-      <c r="H35" s="76"/>
+      <c r="D35" s="77"/>
+      <c r="E35" s="77"/>
+      <c r="F35" s="77"/>
+      <c r="G35" s="77"/>
+      <c r="H35" s="77"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="36" t="s">
@@ -17435,14 +17435,14 @@
       <c r="B36" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C36" s="77" t="s">
+      <c r="C36" s="76" t="s">
         <v>1753</v>
       </c>
-      <c r="D36" s="77"/>
-      <c r="E36" s="77"/>
-      <c r="F36" s="77"/>
-      <c r="G36" s="77"/>
-      <c r="H36" s="77"/>
+      <c r="D36" s="76"/>
+      <c r="E36" s="76"/>
+      <c r="F36" s="76"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="76"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="36" t="s">
@@ -17451,14 +17451,14 @@
       <c r="B37" s="28" t="s">
         <v>1736</v>
       </c>
-      <c r="C37" s="76" t="s">
+      <c r="C37" s="77" t="s">
         <v>1755</v>
       </c>
-      <c r="D37" s="76"/>
-      <c r="E37" s="76"/>
-      <c r="F37" s="76"/>
-      <c r="G37" s="76"/>
-      <c r="H37" s="76"/>
+      <c r="D37" s="77"/>
+      <c r="E37" s="77"/>
+      <c r="F37" s="77"/>
+      <c r="G37" s="77"/>
+      <c r="H37" s="77"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="36" t="s">
@@ -17467,14 +17467,14 @@
       <c r="B38" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C38" s="76" t="s">
+      <c r="C38" s="77" t="s">
         <v>1755</v>
       </c>
-      <c r="D38" s="76"/>
-      <c r="E38" s="76"/>
-      <c r="F38" s="76"/>
-      <c r="G38" s="76"/>
-      <c r="H38" s="76"/>
+      <c r="D38" s="77"/>
+      <c r="E38" s="77"/>
+      <c r="F38" s="77"/>
+      <c r="G38" s="77"/>
+      <c r="H38" s="77"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="36" t="s">
@@ -17483,14 +17483,14 @@
       <c r="B39" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C39" s="77" t="s">
+      <c r="C39" s="76" t="s">
         <v>1753</v>
       </c>
-      <c r="D39" s="77"/>
-      <c r="E39" s="77"/>
-      <c r="F39" s="77"/>
-      <c r="G39" s="77"/>
-      <c r="H39" s="77"/>
+      <c r="D39" s="76"/>
+      <c r="E39" s="76"/>
+      <c r="F39" s="76"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="76"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="36" t="s">
@@ -17499,14 +17499,14 @@
       <c r="B40" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C40" s="77" t="s">
+      <c r="C40" s="76" t="s">
         <v>1753</v>
       </c>
-      <c r="D40" s="77"/>
-      <c r="E40" s="77"/>
-      <c r="F40" s="77"/>
-      <c r="G40" s="77"/>
-      <c r="H40" s="77"/>
+      <c r="D40" s="76"/>
+      <c r="E40" s="76"/>
+      <c r="F40" s="76"/>
+      <c r="G40" s="76"/>
+      <c r="H40" s="76"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="36" t="s">
@@ -17515,14 +17515,14 @@
       <c r="B41" s="28" t="s">
         <v>1737</v>
       </c>
-      <c r="C41" s="77" t="s">
+      <c r="C41" s="76" t="s">
         <v>1759</v>
       </c>
-      <c r="D41" s="77"/>
-      <c r="E41" s="77"/>
-      <c r="F41" s="77"/>
-      <c r="G41" s="77"/>
-      <c r="H41" s="77"/>
+      <c r="D41" s="76"/>
+      <c r="E41" s="76"/>
+      <c r="F41" s="76"/>
+      <c r="G41" s="76"/>
+      <c r="H41" s="76"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="36" t="s">
@@ -17531,14 +17531,14 @@
       <c r="B42" s="28" t="s">
         <v>1738</v>
       </c>
-      <c r="C42" s="77" t="s">
+      <c r="C42" s="76" t="s">
         <v>1761</v>
       </c>
-      <c r="D42" s="77"/>
-      <c r="E42" s="77"/>
-      <c r="F42" s="77"/>
-      <c r="G42" s="77"/>
-      <c r="H42" s="77"/>
+      <c r="D42" s="76"/>
+      <c r="E42" s="76"/>
+      <c r="F42" s="76"/>
+      <c r="G42" s="76"/>
+      <c r="H42" s="76"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="36" t="s">
@@ -17547,14 +17547,14 @@
       <c r="B43" s="28" t="s">
         <v>1739</v>
       </c>
-      <c r="C43" s="77" t="s">
+      <c r="C43" s="76" t="s">
         <v>1763</v>
       </c>
-      <c r="D43" s="77"/>
-      <c r="E43" s="77"/>
-      <c r="F43" s="77"/>
-      <c r="G43" s="77"/>
-      <c r="H43" s="77"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="76"/>
+      <c r="F43" s="76"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="76"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="36" t="s">
@@ -17563,26 +17563,26 @@
       <c r="B44" s="28" t="s">
         <v>1740</v>
       </c>
-      <c r="C44" s="77" t="s">
+      <c r="C44" s="76" t="s">
         <v>1765</v>
       </c>
-      <c r="D44" s="77"/>
-      <c r="E44" s="77"/>
-      <c r="F44" s="77"/>
-      <c r="G44" s="77"/>
-      <c r="H44" s="77"/>
+      <c r="D44" s="76"/>
+      <c r="E44" s="76"/>
+      <c r="F44" s="76"/>
+      <c r="G44" s="76"/>
+      <c r="H44" s="76"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="78" t="s">
+      <c r="A48" s="75" t="s">
         <v>1754</v>
       </c>
-      <c r="B48" s="78"/>
-      <c r="C48" s="78"/>
-      <c r="D48" s="78"/>
-      <c r="E48" s="78"/>
-      <c r="F48" s="78"/>
-      <c r="G48" s="78"/>
-      <c r="H48" s="78"/>
+      <c r="B48" s="75"/>
+      <c r="C48" s="75"/>
+      <c r="D48" s="75"/>
+      <c r="E48" s="75"/>
+      <c r="F48" s="75"/>
+      <c r="G48" s="75"/>
+      <c r="H48" s="75"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
@@ -17595,16 +17595,16 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="78" t="s">
+      <c r="A52" s="75" t="s">
         <v>1756</v>
       </c>
-      <c r="B52" s="78"/>
-      <c r="C52" s="78"/>
-      <c r="D52" s="78"/>
-      <c r="E52" s="78"/>
-      <c r="F52" s="78"/>
-      <c r="G52" s="78"/>
-      <c r="H52" s="78"/>
+      <c r="B52" s="75"/>
+      <c r="C52" s="75"/>
+      <c r="D52" s="75"/>
+      <c r="E52" s="75"/>
+      <c r="F52" s="75"/>
+      <c r="G52" s="75"/>
+      <c r="H52" s="75"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -17612,16 +17612,16 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="78" t="s">
+      <c r="A57" s="75" t="s">
         <v>1769</v>
       </c>
-      <c r="B57" s="78"/>
-      <c r="C57" s="78"/>
-      <c r="D57" s="78"/>
-      <c r="E57" s="78"/>
-      <c r="F57" s="78"/>
-      <c r="G57" s="78"/>
-      <c r="H57" s="78"/>
+      <c r="B57" s="75"/>
+      <c r="C57" s="75"/>
+      <c r="D57" s="75"/>
+      <c r="E57" s="75"/>
+      <c r="F57" s="75"/>
+      <c r="G57" s="75"/>
+      <c r="H57" s="75"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
@@ -17689,12 +17689,12 @@
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H73" s="78" t="s">
+      <c r="H73" s="75" t="s">
         <v>1783</v>
       </c>
-      <c r="I73" s="78"/>
-      <c r="J73" s="78"/>
-      <c r="K73" s="78"/>
+      <c r="I73" s="75"/>
+      <c r="J73" s="75"/>
+      <c r="K73" s="75"/>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="55" t="s">
@@ -18261,6 +18261,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="C32:H32"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="C35:H35"/>
+    <mergeCell ref="C36:H36"/>
+    <mergeCell ref="C37:H37"/>
+    <mergeCell ref="C38:H38"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
+    <mergeCell ref="C41:H41"/>
     <mergeCell ref="A57:H57"/>
     <mergeCell ref="H73:K73"/>
     <mergeCell ref="C42:H42"/>
@@ -18268,16 +18278,6 @@
     <mergeCell ref="C44:H44"/>
     <mergeCell ref="A48:H48"/>
     <mergeCell ref="A52:H52"/>
-    <mergeCell ref="C37:H37"/>
-    <mergeCell ref="C38:H38"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C40:H40"/>
-    <mergeCell ref="C41:H41"/>
-    <mergeCell ref="C32:H32"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="C35:H35"/>
-    <mergeCell ref="C36:H36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -18340,13 +18340,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="75" t="s">
         <v>1905</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
@@ -18499,7 +18499,7 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>2284</v>
+        <v>2304</v>
       </c>
     </row>
   </sheetData>
@@ -22685,10 +22685,10 @@
         <v>2282</v>
       </c>
       <c r="D34" t="s">
+        <v>2284</v>
+      </c>
+      <c r="E34" t="s">
         <v>2285</v>
-      </c>
-      <c r="E34" t="s">
-        <v>2286</v>
       </c>
     </row>
   </sheetData>

--- a/AmbermoonAdvanced.xlsx
+++ b/AmbermoonAdvanced.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Robert\source\repos\Ambermoon-Advanced\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E632F1ED-ED07-4862-B11B-A4827A9C717A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32AA3BA8-3A52-4DA6-8E91-ED082C584105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" firstSheet="39" activeTab="42" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3232" uniqueCount="2312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3248" uniqueCount="2324">
   <si>
     <t>Map texts</t>
   </si>
@@ -7131,6 +7131,42 @@
   </si>
   <si>
     <t>Lava tiles 235-238 block walking and the horse. Green slime (labdata 2 objects 15-17) passable for monsters (2026-10-18)</t>
+  </si>
+  <si>
+    <t>Delay</t>
+  </si>
+  <si>
+    <t>Amiga: yes</t>
+  </si>
+  <si>
+    <t>Party member condition</t>
+  </si>
+  <si>
+    <t>Shake</t>
+  </si>
+  <si>
+    <t>Show map</t>
+  </si>
+  <si>
+    <t>Amiga: implemented 2026-10-18 (was a savegame upgrade placeholder)</t>
+  </si>
+  <si>
+    <t>Toggle switch</t>
+  </si>
+  <si>
+    <t>Amiga: implemented 2026-10-18</t>
+  </si>
+  <si>
+    <t>Dynamic tile change</t>
+  </si>
+  <si>
+    <t>Rectangular exploration</t>
+  </si>
+  <si>
+    <t>Amiga: implemented 2026-10-18 (current map only)</t>
+  </si>
+  <si>
+    <t>Vertical line reveal</t>
   </si>
 </sst>
 </file>
@@ -7776,17 +7812,17 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -17436,14 +17472,14 @@
       <c r="B32" s="54" t="s">
         <v>1745</v>
       </c>
-      <c r="C32" s="75" t="s">
+      <c r="C32" s="78" t="s">
         <v>1746</v>
       </c>
-      <c r="D32" s="75"/>
-      <c r="E32" s="75"/>
-      <c r="F32" s="75"/>
-      <c r="G32" s="75"/>
-      <c r="H32" s="75"/>
+      <c r="D32" s="78"/>
+      <c r="E32" s="78"/>
+      <c r="F32" s="78"/>
+      <c r="G32" s="78"/>
+      <c r="H32" s="78"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="36" t="s">
@@ -17452,14 +17488,14 @@
       <c r="B33" s="28" t="s">
         <v>1748</v>
       </c>
-      <c r="C33" s="76" t="s">
+      <c r="C33" s="77" t="s">
         <v>1749</v>
       </c>
-      <c r="D33" s="76"/>
-      <c r="E33" s="76"/>
-      <c r="F33" s="76"/>
-      <c r="G33" s="76"/>
-      <c r="H33" s="76"/>
+      <c r="D33" s="77"/>
+      <c r="E33" s="77"/>
+      <c r="F33" s="77"/>
+      <c r="G33" s="77"/>
+      <c r="H33" s="77"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="36" t="s">
@@ -17468,14 +17504,14 @@
       <c r="B34" s="28" t="s">
         <v>1748</v>
       </c>
-      <c r="C34" s="76" t="s">
+      <c r="C34" s="77" t="s">
         <v>1749</v>
       </c>
-      <c r="D34" s="76"/>
-      <c r="E34" s="76"/>
-      <c r="F34" s="76"/>
-      <c r="G34" s="76"/>
-      <c r="H34" s="76"/>
+      <c r="D34" s="77"/>
+      <c r="E34" s="77"/>
+      <c r="F34" s="77"/>
+      <c r="G34" s="77"/>
+      <c r="H34" s="77"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="36" t="s">
@@ -17484,14 +17520,14 @@
       <c r="B35" s="28" t="s">
         <v>1748</v>
       </c>
-      <c r="C35" s="76" t="s">
+      <c r="C35" s="77" t="s">
         <v>1749</v>
       </c>
-      <c r="D35" s="76"/>
-      <c r="E35" s="76"/>
-      <c r="F35" s="76"/>
-      <c r="G35" s="76"/>
-      <c r="H35" s="76"/>
+      <c r="D35" s="77"/>
+      <c r="E35" s="77"/>
+      <c r="F35" s="77"/>
+      <c r="G35" s="77"/>
+      <c r="H35" s="77"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="36" t="s">
@@ -17500,14 +17536,14 @@
       <c r="B36" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C36" s="77" t="s">
+      <c r="C36" s="76" t="s">
         <v>1753</v>
       </c>
-      <c r="D36" s="77"/>
-      <c r="E36" s="77"/>
-      <c r="F36" s="77"/>
-      <c r="G36" s="77"/>
-      <c r="H36" s="77"/>
+      <c r="D36" s="76"/>
+      <c r="E36" s="76"/>
+      <c r="F36" s="76"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="76"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="36" t="s">
@@ -17516,14 +17552,14 @@
       <c r="B37" s="28" t="s">
         <v>1736</v>
       </c>
-      <c r="C37" s="76" t="s">
+      <c r="C37" s="77" t="s">
         <v>1755</v>
       </c>
-      <c r="D37" s="76"/>
-      <c r="E37" s="76"/>
-      <c r="F37" s="76"/>
-      <c r="G37" s="76"/>
-      <c r="H37" s="76"/>
+      <c r="D37" s="77"/>
+      <c r="E37" s="77"/>
+      <c r="F37" s="77"/>
+      <c r="G37" s="77"/>
+      <c r="H37" s="77"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="36" t="s">
@@ -17532,14 +17568,14 @@
       <c r="B38" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C38" s="76" t="s">
+      <c r="C38" s="77" t="s">
         <v>1755</v>
       </c>
-      <c r="D38" s="76"/>
-      <c r="E38" s="76"/>
-      <c r="F38" s="76"/>
-      <c r="G38" s="76"/>
-      <c r="H38" s="76"/>
+      <c r="D38" s="77"/>
+      <c r="E38" s="77"/>
+      <c r="F38" s="77"/>
+      <c r="G38" s="77"/>
+      <c r="H38" s="77"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="36" t="s">
@@ -17548,14 +17584,14 @@
       <c r="B39" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C39" s="77" t="s">
+      <c r="C39" s="76" t="s">
         <v>1753</v>
       </c>
-      <c r="D39" s="77"/>
-      <c r="E39" s="77"/>
-      <c r="F39" s="77"/>
-      <c r="G39" s="77"/>
-      <c r="H39" s="77"/>
+      <c r="D39" s="76"/>
+      <c r="E39" s="76"/>
+      <c r="F39" s="76"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="76"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="36" t="s">
@@ -17564,14 +17600,14 @@
       <c r="B40" s="28" t="s">
         <v>1734</v>
       </c>
-      <c r="C40" s="77" t="s">
+      <c r="C40" s="76" t="s">
         <v>1753</v>
       </c>
-      <c r="D40" s="77"/>
-      <c r="E40" s="77"/>
-      <c r="F40" s="77"/>
-      <c r="G40" s="77"/>
-      <c r="H40" s="77"/>
+      <c r="D40" s="76"/>
+      <c r="E40" s="76"/>
+      <c r="F40" s="76"/>
+      <c r="G40" s="76"/>
+      <c r="H40" s="76"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="36" t="s">
@@ -17580,14 +17616,14 @@
       <c r="B41" s="28" t="s">
         <v>1737</v>
       </c>
-      <c r="C41" s="77" t="s">
+      <c r="C41" s="76" t="s">
         <v>1759</v>
       </c>
-      <c r="D41" s="77"/>
-      <c r="E41" s="77"/>
-      <c r="F41" s="77"/>
-      <c r="G41" s="77"/>
-      <c r="H41" s="77"/>
+      <c r="D41" s="76"/>
+      <c r="E41" s="76"/>
+      <c r="F41" s="76"/>
+      <c r="G41" s="76"/>
+      <c r="H41" s="76"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="36" t="s">
@@ -17596,14 +17632,14 @@
       <c r="B42" s="28" t="s">
         <v>1738</v>
       </c>
-      <c r="C42" s="77" t="s">
+      <c r="C42" s="76" t="s">
         <v>1761</v>
       </c>
-      <c r="D42" s="77"/>
-      <c r="E42" s="77"/>
-      <c r="F42" s="77"/>
-      <c r="G42" s="77"/>
-      <c r="H42" s="77"/>
+      <c r="D42" s="76"/>
+      <c r="E42" s="76"/>
+      <c r="F42" s="76"/>
+      <c r="G42" s="76"/>
+      <c r="H42" s="76"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="36" t="s">
@@ -17612,14 +17648,14 @@
       <c r="B43" s="28" t="s">
         <v>1739</v>
       </c>
-      <c r="C43" s="77" t="s">
+      <c r="C43" s="76" t="s">
         <v>1763</v>
       </c>
-      <c r="D43" s="77"/>
-      <c r="E43" s="77"/>
-      <c r="F43" s="77"/>
-      <c r="G43" s="77"/>
-      <c r="H43" s="77"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="76"/>
+      <c r="F43" s="76"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="76"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="36" t="s">
@@ -17628,26 +17664,26 @@
       <c r="B44" s="28" t="s">
         <v>1740</v>
       </c>
-      <c r="C44" s="77" t="s">
+      <c r="C44" s="76" t="s">
         <v>1765</v>
       </c>
-      <c r="D44" s="77"/>
-      <c r="E44" s="77"/>
-      <c r="F44" s="77"/>
-      <c r="G44" s="77"/>
-      <c r="H44" s="77"/>
+      <c r="D44" s="76"/>
+      <c r="E44" s="76"/>
+      <c r="F44" s="76"/>
+      <c r="G44" s="76"/>
+      <c r="H44" s="76"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A48" s="78" t="s">
+      <c r="A48" s="75" t="s">
         <v>1754</v>
       </c>
-      <c r="B48" s="78"/>
-      <c r="C48" s="78"/>
-      <c r="D48" s="78"/>
-      <c r="E48" s="78"/>
-      <c r="F48" s="78"/>
-      <c r="G48" s="78"/>
-      <c r="H48" s="78"/>
+      <c r="B48" s="75"/>
+      <c r="C48" s="75"/>
+      <c r="D48" s="75"/>
+      <c r="E48" s="75"/>
+      <c r="F48" s="75"/>
+      <c r="G48" s="75"/>
+      <c r="H48" s="75"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
@@ -17660,16 +17696,16 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A52" s="78" t="s">
+      <c r="A52" s="75" t="s">
         <v>1756</v>
       </c>
-      <c r="B52" s="78"/>
-      <c r="C52" s="78"/>
-      <c r="D52" s="78"/>
-      <c r="E52" s="78"/>
-      <c r="F52" s="78"/>
-      <c r="G52" s="78"/>
-      <c r="H52" s="78"/>
+      <c r="B52" s="75"/>
+      <c r="C52" s="75"/>
+      <c r="D52" s="75"/>
+      <c r="E52" s="75"/>
+      <c r="F52" s="75"/>
+      <c r="G52" s="75"/>
+      <c r="H52" s="75"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
@@ -17677,16 +17713,16 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A57" s="78" t="s">
+      <c r="A57" s="75" t="s">
         <v>1769</v>
       </c>
-      <c r="B57" s="78"/>
-      <c r="C57" s="78"/>
-      <c r="D57" s="78"/>
-      <c r="E57" s="78"/>
-      <c r="F57" s="78"/>
-      <c r="G57" s="78"/>
-      <c r="H57" s="78"/>
+      <c r="B57" s="75"/>
+      <c r="C57" s="75"/>
+      <c r="D57" s="75"/>
+      <c r="E57" s="75"/>
+      <c r="F57" s="75"/>
+      <c r="G57" s="75"/>
+      <c r="H57" s="75"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
@@ -17754,12 +17790,12 @@
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="H73" s="78" t="s">
+      <c r="H73" s="75" t="s">
         <v>1783</v>
       </c>
-      <c r="I73" s="78"/>
-      <c r="J73" s="78"/>
-      <c r="K73" s="78"/>
+      <c r="I73" s="75"/>
+      <c r="J73" s="75"/>
+      <c r="K73" s="75"/>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74" s="55" t="s">
@@ -18326,6 +18362,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="C32:H32"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="C35:H35"/>
+    <mergeCell ref="C36:H36"/>
+    <mergeCell ref="C37:H37"/>
+    <mergeCell ref="C38:H38"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
+    <mergeCell ref="C41:H41"/>
     <mergeCell ref="A57:H57"/>
     <mergeCell ref="H73:K73"/>
     <mergeCell ref="C42:H42"/>
@@ -18333,16 +18379,6 @@
     <mergeCell ref="C44:H44"/>
     <mergeCell ref="A48:H48"/>
     <mergeCell ref="A52:H52"/>
-    <mergeCell ref="C37:H37"/>
-    <mergeCell ref="C38:H38"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C40:H40"/>
-    <mergeCell ref="C41:H41"/>
-    <mergeCell ref="C32:H32"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="C35:H35"/>
-    <mergeCell ref="C36:H36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -18405,13 +18441,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="75" t="s">
         <v>1905</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="56" t="s">
@@ -18625,6 +18661,15 @@
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2312</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2313</v>
+      </c>
       <c r="E3">
         <v>22</v>
       </c>
@@ -18636,6 +18681,15 @@
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2314</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2313</v>
+      </c>
       <c r="E4">
         <v>23</v>
       </c>
@@ -18647,6 +18701,15 @@
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2315</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2313</v>
+      </c>
       <c r="E5">
         <v>24</v>
       </c>
@@ -18658,26 +18721,71 @@
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2316</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2317</v>
+      </c>
       <c r="I6" t="s">
         <v>1935</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2318</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2319</v>
+      </c>
       <c r="I7" t="s">
         <v>1936</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
+        <v>2320</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2319</v>
+      </c>
       <c r="I8" t="s">
         <v>1937</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2321</v>
+      </c>
+      <c r="C9" t="s">
+        <v>2322</v>
+      </c>
       <c r="I9" t="s">
         <v>1938</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2323</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2319</v>
+      </c>
       <c r="I10" t="s">
         <v>1939</v>
       </c>
